--- a/artfynd/A 34441-2025 artfynd.xlsx
+++ b/artfynd/A 34441-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127497133</v>
+        <v>127497136</v>
       </c>
       <c r="B2" t="n">
-        <v>79014</v>
+        <v>92620</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>865224</v>
+        <v>864673</v>
       </c>
       <c r="R2" t="n">
-        <v>7494121</v>
+        <v>7493901</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127497134</v>
+        <v>127497133</v>
       </c>
       <c r="B3" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>865012</v>
+        <v>865224</v>
       </c>
       <c r="R3" t="n">
-        <v>7493915</v>
+        <v>7494121</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127497136</v>
+        <v>127497100</v>
       </c>
       <c r="B4" t="n">
-        <v>92616</v>
+        <v>80025</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6456</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>864673</v>
+        <v>864814</v>
       </c>
       <c r="R4" t="n">
-        <v>7493901</v>
+        <v>7494119</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127497110</v>
+        <v>127497134</v>
       </c>
       <c r="B5" t="n">
-        <v>80153</v>
+        <v>79018</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>865019</v>
+        <v>865012</v>
       </c>
       <c r="R5" t="n">
-        <v>7494142</v>
+        <v>7493915</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127497100</v>
+        <v>127497110</v>
       </c>
       <c r="B6" t="n">
-        <v>80021</v>
+        <v>80157</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>6464</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>864814</v>
+        <v>865019</v>
       </c>
       <c r="R6" t="n">
-        <v>7494119</v>
+        <v>7494142</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1163,7 +1163,7 @@
         <v>127497116</v>
       </c>
       <c r="B7" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>127497109</v>
       </c>
       <c r="B8" t="n">
-        <v>80153</v>
+        <v>80157</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127497118</v>
+        <v>127497142</v>
       </c>
       <c r="B9" t="n">
-        <v>79014</v>
+        <v>77996</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>864875</v>
+        <v>864722</v>
       </c>
       <c r="R9" t="n">
-        <v>7493981</v>
+        <v>7493992</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127497142</v>
+        <v>127497118</v>
       </c>
       <c r="B10" t="n">
-        <v>77992</v>
+        <v>79018</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>864722</v>
+        <v>864875</v>
       </c>
       <c r="R10" t="n">
-        <v>7493992</v>
+        <v>7493981</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1551,7 +1551,7 @@
         <v>127497141</v>
       </c>
       <c r="B11" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>127497126</v>
       </c>
       <c r="B12" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>127497144</v>
       </c>
       <c r="B13" t="n">
-        <v>78420</v>
+        <v>78424</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>127497093</v>
       </c>
       <c r="B14" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>127497111</v>
       </c>
       <c r="B15" t="n">
-        <v>58027</v>
+        <v>58031</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>127497114</v>
       </c>
       <c r="B16" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>127497115</v>
       </c>
       <c r="B17" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>127497117</v>
       </c>
       <c r="B18" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127497120</v>
+        <v>127497145</v>
       </c>
       <c r="B19" t="n">
-        <v>79014</v>
+        <v>78424</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2335,21 +2335,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>864828</v>
+        <v>865232</v>
       </c>
       <c r="R19" t="n">
-        <v>7494091</v>
+        <v>7494161</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2421,10 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127497145</v>
+        <v>127497120</v>
       </c>
       <c r="B20" t="n">
-        <v>78420</v>
+        <v>79018</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2432,21 +2432,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>865232</v>
+        <v>864828</v>
       </c>
       <c r="R20" t="n">
-        <v>7494161</v>
+        <v>7494091</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2521,7 +2521,7 @@
         <v>127497107</v>
       </c>
       <c r="B21" t="n">
-        <v>97327</v>
+        <v>97331</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2615,10 +2615,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127497143</v>
+        <v>127497132</v>
       </c>
       <c r="B22" t="n">
-        <v>92610</v>
+        <v>79018</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2626,21 +2626,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4362</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>865176</v>
+        <v>865208</v>
       </c>
       <c r="R22" t="n">
-        <v>7494463</v>
+        <v>7494123</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2715,7 +2715,7 @@
         <v>127497099</v>
       </c>
       <c r="B23" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2809,10 +2809,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127497132</v>
+        <v>127497143</v>
       </c>
       <c r="B24" t="n">
-        <v>79014</v>
+        <v>92614</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2820,21 +2820,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>865208</v>
+        <v>865176</v>
       </c>
       <c r="R24" t="n">
-        <v>7494123</v>
+        <v>7494463</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2909,7 +2909,7 @@
         <v>127497130</v>
       </c>
       <c r="B25" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>127497108</v>
       </c>
       <c r="B26" t="n">
-        <v>97327</v>
+        <v>97331</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3100,10 +3100,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127497097</v>
+        <v>127497127</v>
       </c>
       <c r="B27" t="n">
-        <v>57657</v>
+        <v>79018</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3111,21 +3111,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3135,10 +3135,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>865211</v>
+        <v>865064</v>
       </c>
       <c r="R27" t="n">
-        <v>7494097</v>
+        <v>7494185</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3197,10 +3197,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127497127</v>
+        <v>127497097</v>
       </c>
       <c r="B28" t="n">
-        <v>79014</v>
+        <v>57661</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3208,21 +3208,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3232,10 +3232,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>865064</v>
+        <v>865211</v>
       </c>
       <c r="R28" t="n">
-        <v>7494185</v>
+        <v>7494097</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3297,7 +3297,7 @@
         <v>127497137</v>
       </c>
       <c r="B29" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3394,7 +3394,7 @@
         <v>127497131</v>
       </c>
       <c r="B30" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>127497135</v>
       </c>
       <c r="B31" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>127497119</v>
       </c>
       <c r="B32" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         <v>127497096</v>
       </c>
       <c r="B33" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3779,10 +3779,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127497123</v>
+        <v>127497129</v>
       </c>
       <c r="B34" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3814,10 +3814,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>864943</v>
+        <v>865084</v>
       </c>
       <c r="R34" t="n">
-        <v>7494130</v>
+        <v>7494368</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3876,10 +3876,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127497129</v>
+        <v>127497123</v>
       </c>
       <c r="B35" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3911,10 +3911,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>865084</v>
+        <v>864943</v>
       </c>
       <c r="R35" t="n">
-        <v>7494368</v>
+        <v>7494130</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -3973,32 +3973,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127497122</v>
+        <v>127497140</v>
       </c>
       <c r="B36" t="n">
-        <v>79014</v>
+        <v>92620</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4008,10 +4008,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>864916</v>
+        <v>865254</v>
       </c>
       <c r="R36" t="n">
-        <v>7494217</v>
+        <v>7494165</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4070,32 +4070,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127497140</v>
+        <v>127497122</v>
       </c>
       <c r="B37" t="n">
-        <v>92616</v>
+        <v>79018</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4105,10 +4105,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>865254</v>
+        <v>864916</v>
       </c>
       <c r="R37" t="n">
-        <v>7494165</v>
+        <v>7494217</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4167,10 +4167,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127497105</v>
+        <v>127497106</v>
       </c>
       <c r="B38" t="n">
-        <v>97327</v>
+        <v>97331</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4202,10 +4202,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>864754</v>
+        <v>864869</v>
       </c>
       <c r="R38" t="n">
-        <v>7493961</v>
+        <v>7494274</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4264,10 +4264,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127497106</v>
+        <v>127497105</v>
       </c>
       <c r="B39" t="n">
-        <v>97327</v>
+        <v>97331</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4299,10 +4299,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>864869</v>
+        <v>864754</v>
       </c>
       <c r="R39" t="n">
-        <v>7494274</v>
+        <v>7493961</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4361,10 +4361,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127497124</v>
+        <v>127497128</v>
       </c>
       <c r="B40" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4396,10 +4396,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>864971</v>
+        <v>864973</v>
       </c>
       <c r="R40" t="n">
-        <v>7494087</v>
+        <v>7494288</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4458,10 +4458,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127497128</v>
+        <v>127497125</v>
       </c>
       <c r="B41" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4493,10 +4493,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>864973</v>
+        <v>864993</v>
       </c>
       <c r="R41" t="n">
-        <v>7494288</v>
+        <v>7494054</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4555,10 +4555,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127497125</v>
+        <v>127497124</v>
       </c>
       <c r="B42" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4590,10 +4590,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>864993</v>
+        <v>864971</v>
       </c>
       <c r="R42" t="n">
-        <v>7494054</v>
+        <v>7494087</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>

--- a/artfynd/A 34441-2025 artfynd.xlsx
+++ b/artfynd/A 34441-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127497136</v>
+        <v>127497133</v>
       </c>
       <c r="B2" t="n">
-        <v>92620</v>
+        <v>79018</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>864673</v>
+        <v>865224</v>
       </c>
       <c r="R2" t="n">
-        <v>7493901</v>
+        <v>7494121</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127497133</v>
+        <v>127497100</v>
       </c>
       <c r="B3" t="n">
-        <v>79018</v>
+        <v>80025</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>865224</v>
+        <v>864814</v>
       </c>
       <c r="R3" t="n">
-        <v>7494121</v>
+        <v>7494119</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127497100</v>
+        <v>127497134</v>
       </c>
       <c r="B4" t="n">
-        <v>80025</v>
+        <v>79018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>864814</v>
+        <v>865012</v>
       </c>
       <c r="R4" t="n">
-        <v>7494119</v>
+        <v>7493915</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127497134</v>
+        <v>127497110</v>
       </c>
       <c r="B5" t="n">
-        <v>79018</v>
+        <v>80157</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>865012</v>
+        <v>865019</v>
       </c>
       <c r="R5" t="n">
-        <v>7493915</v>
+        <v>7494142</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127497110</v>
+        <v>127497136</v>
       </c>
       <c r="B6" t="n">
-        <v>80157</v>
+        <v>92620</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6464</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>865019</v>
+        <v>864673</v>
       </c>
       <c r="R6" t="n">
-        <v>7494142</v>
+        <v>7493901</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127497109</v>
+        <v>127497118</v>
       </c>
       <c r="B8" t="n">
-        <v>80157</v>
+        <v>79018</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>864826</v>
+        <v>864875</v>
       </c>
       <c r="R8" t="n">
-        <v>7494067</v>
+        <v>7493981</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1354,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127497142</v>
+        <v>127497109</v>
       </c>
       <c r="B9" t="n">
-        <v>77996</v>
+        <v>80157</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6487</v>
+        <v>6464</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>864722</v>
+        <v>864826</v>
       </c>
       <c r="R9" t="n">
-        <v>7493992</v>
+        <v>7494067</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127497118</v>
+        <v>127497142</v>
       </c>
       <c r="B10" t="n">
-        <v>79018</v>
+        <v>77996</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>864875</v>
+        <v>864722</v>
       </c>
       <c r="R10" t="n">
-        <v>7493981</v>
+        <v>7493992</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127497141</v>
+        <v>127497144</v>
       </c>
       <c r="B11" t="n">
-        <v>92620</v>
+        <v>78424</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>865108</v>
+        <v>864722</v>
       </c>
       <c r="R11" t="n">
-        <v>7493903</v>
+        <v>7493995</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127497126</v>
+        <v>127497141</v>
       </c>
       <c r="B12" t="n">
-        <v>79018</v>
+        <v>92620</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>865024</v>
+        <v>865108</v>
       </c>
       <c r="R12" t="n">
-        <v>7494051</v>
+        <v>7493903</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127497144</v>
+        <v>127497126</v>
       </c>
       <c r="B13" t="n">
-        <v>78424</v>
+        <v>79018</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>864722</v>
+        <v>865024</v>
       </c>
       <c r="R13" t="n">
-        <v>7493995</v>
+        <v>7494051</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2227,7 +2227,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127497117</v>
+        <v>127497120</v>
       </c>
       <c r="B18" t="n">
         <v>79018</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>864891</v>
+        <v>864828</v>
       </c>
       <c r="R18" t="n">
-        <v>7493944</v>
+        <v>7494091</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127497145</v>
+        <v>127497117</v>
       </c>
       <c r="B19" t="n">
-        <v>78424</v>
+        <v>79018</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2335,21 +2335,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>865232</v>
+        <v>864891</v>
       </c>
       <c r="R19" t="n">
-        <v>7494161</v>
+        <v>7493944</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2421,10 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127497120</v>
+        <v>127497145</v>
       </c>
       <c r="B20" t="n">
-        <v>79018</v>
+        <v>78424</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2432,21 +2432,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>864828</v>
+        <v>865232</v>
       </c>
       <c r="R20" t="n">
-        <v>7494091</v>
+        <v>7494161</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3294,32 +3294,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127497137</v>
+        <v>127497131</v>
       </c>
       <c r="B29" t="n">
-        <v>92620</v>
+        <v>79018</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3329,10 +3329,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>864714</v>
+        <v>865118</v>
       </c>
       <c r="R29" t="n">
-        <v>7493998</v>
+        <v>7494428</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3391,32 +3391,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127497131</v>
+        <v>127497137</v>
       </c>
       <c r="B30" t="n">
-        <v>79018</v>
+        <v>92620</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3426,10 +3426,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>865118</v>
+        <v>864714</v>
       </c>
       <c r="R30" t="n">
-        <v>7494428</v>
+        <v>7493998</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3488,32 +3488,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127497135</v>
+        <v>127497096</v>
       </c>
       <c r="B31" t="n">
-        <v>92620</v>
+        <v>57661</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3523,10 +3523,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>864717</v>
+        <v>864944</v>
       </c>
       <c r="R31" t="n">
-        <v>7493817</v>
+        <v>7494143</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3682,32 +3682,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127497096</v>
+        <v>127497135</v>
       </c>
       <c r="B33" t="n">
-        <v>57661</v>
+        <v>92620</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3717,10 +3717,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>864944</v>
+        <v>864717</v>
       </c>
       <c r="R33" t="n">
-        <v>7494143</v>
+        <v>7493817</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3973,32 +3973,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127497140</v>
+        <v>127497122</v>
       </c>
       <c r="B36" t="n">
-        <v>92620</v>
+        <v>79018</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4008,10 +4008,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>865254</v>
+        <v>864916</v>
       </c>
       <c r="R36" t="n">
-        <v>7494165</v>
+        <v>7494217</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4070,32 +4070,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127497122</v>
+        <v>127497140</v>
       </c>
       <c r="B37" t="n">
-        <v>79018</v>
+        <v>92620</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4105,10 +4105,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>864916</v>
+        <v>865254</v>
       </c>
       <c r="R37" t="n">
-        <v>7494217</v>
+        <v>7494165</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>

--- a/artfynd/A 34441-2025 artfynd.xlsx
+++ b/artfynd/A 34441-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY42"/>
+  <dimension ref="A1:AY44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2227,7 +2227,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127497120</v>
+        <v>127497117</v>
       </c>
       <c r="B18" t="n">
         <v>79018</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>864828</v>
+        <v>864891</v>
       </c>
       <c r="R18" t="n">
-        <v>7494091</v>
+        <v>7493944</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127497117</v>
+        <v>127497145</v>
       </c>
       <c r="B19" t="n">
-        <v>79018</v>
+        <v>78424</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2335,21 +2335,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>864891</v>
+        <v>865232</v>
       </c>
       <c r="R19" t="n">
-        <v>7493944</v>
+        <v>7494161</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2421,10 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127497145</v>
+        <v>127497120</v>
       </c>
       <c r="B20" t="n">
-        <v>78424</v>
+        <v>79018</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2432,21 +2432,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>865232</v>
+        <v>864828</v>
       </c>
       <c r="R20" t="n">
-        <v>7494161</v>
+        <v>7494091</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3197,10 +3197,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127497097</v>
+        <v>127497131</v>
       </c>
       <c r="B28" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3208,21 +3208,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3232,10 +3232,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>865211</v>
+        <v>865118</v>
       </c>
       <c r="R28" t="n">
-        <v>7494097</v>
+        <v>7494428</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3294,32 +3294,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127497131</v>
+        <v>127497137</v>
       </c>
       <c r="B29" t="n">
-        <v>79018</v>
+        <v>92620</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3329,10 +3329,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>865118</v>
+        <v>864714</v>
       </c>
       <c r="R29" t="n">
-        <v>7494428</v>
+        <v>7493998</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3391,32 +3391,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127497137</v>
+        <v>127497119</v>
       </c>
       <c r="B30" t="n">
-        <v>92620</v>
+        <v>79018</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3426,10 +3426,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>864714</v>
+        <v>864839</v>
       </c>
       <c r="R30" t="n">
-        <v>7493998</v>
+        <v>7494049</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3488,32 +3488,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127497096</v>
+        <v>127497135</v>
       </c>
       <c r="B31" t="n">
-        <v>57661</v>
+        <v>92620</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3523,10 +3523,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>864944</v>
+        <v>864717</v>
       </c>
       <c r="R31" t="n">
-        <v>7494143</v>
+        <v>7493817</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3585,7 +3585,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127497119</v>
+        <v>127497129</v>
       </c>
       <c r="B32" t="n">
         <v>79018</v>
@@ -3620,10 +3620,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>864839</v>
+        <v>865084</v>
       </c>
       <c r="R32" t="n">
-        <v>7494049</v>
+        <v>7494368</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3682,32 +3682,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127497135</v>
+        <v>127497123</v>
       </c>
       <c r="B33" t="n">
-        <v>92620</v>
+        <v>79018</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3717,10 +3717,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>864717</v>
+        <v>864943</v>
       </c>
       <c r="R33" t="n">
-        <v>7493817</v>
+        <v>7494130</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3779,32 +3779,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127497129</v>
+        <v>127497140</v>
       </c>
       <c r="B34" t="n">
-        <v>79018</v>
+        <v>92620</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3814,10 +3814,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>865084</v>
+        <v>865254</v>
       </c>
       <c r="R34" t="n">
-        <v>7494368</v>
+        <v>7494165</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3876,7 +3876,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127497123</v>
+        <v>127497122</v>
       </c>
       <c r="B35" t="n">
         <v>79018</v>
@@ -3911,10 +3911,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>864943</v>
+        <v>864916</v>
       </c>
       <c r="R35" t="n">
-        <v>7494130</v>
+        <v>7494217</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -3973,32 +3973,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127497122</v>
+        <v>127497106</v>
       </c>
       <c r="B36" t="n">
-        <v>79018</v>
+        <v>97331</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4008,10 +4008,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>864916</v>
+        <v>864869</v>
       </c>
       <c r="R36" t="n">
-        <v>7494217</v>
+        <v>7494274</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4070,10 +4070,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127497140</v>
+        <v>127497105</v>
       </c>
       <c r="B37" t="n">
-        <v>92620</v>
+        <v>97331</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4081,21 +4081,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4105,10 +4105,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>865254</v>
+        <v>864754</v>
       </c>
       <c r="R37" t="n">
-        <v>7494165</v>
+        <v>7493961</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4167,32 +4167,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127497106</v>
+        <v>127497128</v>
       </c>
       <c r="B38" t="n">
-        <v>97331</v>
+        <v>79018</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4202,10 +4202,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>864869</v>
+        <v>864973</v>
       </c>
       <c r="R38" t="n">
-        <v>7494274</v>
+        <v>7494288</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4264,32 +4264,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127497105</v>
+        <v>127497125</v>
       </c>
       <c r="B39" t="n">
-        <v>97331</v>
+        <v>79018</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4299,10 +4299,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>864754</v>
+        <v>864993</v>
       </c>
       <c r="R39" t="n">
-        <v>7493961</v>
+        <v>7494054</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4361,7 +4361,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127497128</v>
+        <v>127497124</v>
       </c>
       <c r="B40" t="n">
         <v>79018</v>
@@ -4396,10 +4396,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>864973</v>
+        <v>864971</v>
       </c>
       <c r="R40" t="n">
-        <v>7494288</v>
+        <v>7494087</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4458,10 +4458,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127497125</v>
+        <v>127497103</v>
       </c>
       <c r="B41" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4469,34 +4469,38 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Honkavaara, Nb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>864993</v>
+        <v>865216</v>
       </c>
       <c r="R41" t="n">
-        <v>7494054</v>
+        <v>7494100</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4529,6 +4533,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, äldre.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4555,10 +4564,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127497124</v>
+        <v>127497098</v>
       </c>
       <c r="B42" t="n">
-        <v>79018</v>
+        <v>91350</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4566,34 +4575,38 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Honkavaara, Nb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>864971</v>
+        <v>864846</v>
       </c>
       <c r="R42" t="n">
-        <v>7494087</v>
+        <v>7494223</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4634,6 +4647,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4649,6 +4663,222 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>127497097</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Honkavaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>865211</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7494097</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>127497096</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Honkavaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>864944</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7494143</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Färskt ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34441-2025 artfynd.xlsx
+++ b/artfynd/A 34441-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127497133</v>
+        <v>127497100</v>
       </c>
       <c r="B2" t="n">
-        <v>79018</v>
+        <v>80025</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>865224</v>
+        <v>864814</v>
       </c>
       <c r="R2" t="n">
-        <v>7494121</v>
+        <v>7494119</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127497100</v>
+        <v>127497110</v>
       </c>
       <c r="B3" t="n">
-        <v>80025</v>
+        <v>80157</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>6464</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>864814</v>
+        <v>865019</v>
       </c>
       <c r="R3" t="n">
-        <v>7494119</v>
+        <v>7494142</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127497134</v>
+        <v>127497136</v>
       </c>
       <c r="B4" t="n">
-        <v>79018</v>
+        <v>92620</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>865012</v>
+        <v>864673</v>
       </c>
       <c r="R4" t="n">
-        <v>7493915</v>
+        <v>7493901</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127497110</v>
+        <v>127497133</v>
       </c>
       <c r="B5" t="n">
-        <v>80157</v>
+        <v>79018</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>865019</v>
+        <v>865224</v>
       </c>
       <c r="R5" t="n">
-        <v>7494142</v>
+        <v>7494121</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127497136</v>
+        <v>127497134</v>
       </c>
       <c r="B6" t="n">
-        <v>92620</v>
+        <v>79018</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>864673</v>
+        <v>865012</v>
       </c>
       <c r="R6" t="n">
-        <v>7493901</v>
+        <v>7493915</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127497118</v>
+        <v>127497109</v>
       </c>
       <c r="B8" t="n">
-        <v>79018</v>
+        <v>80157</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>864875</v>
+        <v>864826</v>
       </c>
       <c r="R8" t="n">
-        <v>7493981</v>
+        <v>7494067</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1354,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127497109</v>
+        <v>127497142</v>
       </c>
       <c r="B9" t="n">
-        <v>80157</v>
+        <v>77996</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6464</v>
+        <v>6487</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>864826</v>
+        <v>864722</v>
       </c>
       <c r="R9" t="n">
-        <v>7494067</v>
+        <v>7493992</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127497142</v>
+        <v>127497118</v>
       </c>
       <c r="B10" t="n">
-        <v>77996</v>
+        <v>79018</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>864722</v>
+        <v>864875</v>
       </c>
       <c r="R10" t="n">
-        <v>7493992</v>
+        <v>7493981</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127497144</v>
+        <v>127497141</v>
       </c>
       <c r="B11" t="n">
-        <v>78424</v>
+        <v>92620</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>864722</v>
+        <v>865108</v>
       </c>
       <c r="R11" t="n">
-        <v>7493995</v>
+        <v>7493903</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127497141</v>
+        <v>127497126</v>
       </c>
       <c r="B12" t="n">
-        <v>92620</v>
+        <v>79018</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>865108</v>
+        <v>865024</v>
       </c>
       <c r="R12" t="n">
-        <v>7493903</v>
+        <v>7494051</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127497126</v>
+        <v>127497144</v>
       </c>
       <c r="B13" t="n">
-        <v>79018</v>
+        <v>78424</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>865024</v>
+        <v>864722</v>
       </c>
       <c r="R13" t="n">
-        <v>7494051</v>
+        <v>7493995</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2615,10 +2615,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127497132</v>
+        <v>127497143</v>
       </c>
       <c r="B22" t="n">
-        <v>79018</v>
+        <v>92614</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2626,21 +2626,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>865208</v>
+        <v>865176</v>
       </c>
       <c r="R22" t="n">
-        <v>7494123</v>
+        <v>7494463</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2712,10 +2712,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127497099</v>
+        <v>127497132</v>
       </c>
       <c r="B23" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2723,21 +2723,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2747,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>865213</v>
+        <v>865208</v>
       </c>
       <c r="R23" t="n">
-        <v>7494422</v>
+        <v>7494123</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2809,10 +2809,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127497143</v>
+        <v>127497099</v>
       </c>
       <c r="B24" t="n">
-        <v>92614</v>
+        <v>57658</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2820,21 +2820,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4362</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>865176</v>
+        <v>865213</v>
       </c>
       <c r="R24" t="n">
-        <v>7494463</v>
+        <v>7494422</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3197,32 +3197,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127497131</v>
+        <v>127497137</v>
       </c>
       <c r="B28" t="n">
-        <v>79018</v>
+        <v>92620</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3232,10 +3232,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>865118</v>
+        <v>864714</v>
       </c>
       <c r="R28" t="n">
-        <v>7494428</v>
+        <v>7493998</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3294,32 +3294,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127497137</v>
+        <v>127497131</v>
       </c>
       <c r="B29" t="n">
-        <v>92620</v>
+        <v>79018</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3329,10 +3329,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>864714</v>
+        <v>865118</v>
       </c>
       <c r="R29" t="n">
-        <v>7493998</v>
+        <v>7494428</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3391,32 +3391,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127497119</v>
+        <v>127497135</v>
       </c>
       <c r="B30" t="n">
-        <v>79018</v>
+        <v>92620</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3426,10 +3426,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>864839</v>
+        <v>864717</v>
       </c>
       <c r="R30" t="n">
-        <v>7494049</v>
+        <v>7493817</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3488,32 +3488,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127497135</v>
+        <v>127497119</v>
       </c>
       <c r="B31" t="n">
-        <v>92620</v>
+        <v>79018</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3523,10 +3523,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>864717</v>
+        <v>864839</v>
       </c>
       <c r="R31" t="n">
-        <v>7493817</v>
+        <v>7494049</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3973,7 +3973,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127497106</v>
+        <v>127497105</v>
       </c>
       <c r="B36" t="n">
         <v>97331</v>
@@ -4008,10 +4008,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>864869</v>
+        <v>864754</v>
       </c>
       <c r="R36" t="n">
-        <v>7494274</v>
+        <v>7493961</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4070,7 +4070,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127497105</v>
+        <v>127497106</v>
       </c>
       <c r="B37" t="n">
         <v>97331</v>
@@ -4105,10 +4105,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>864754</v>
+        <v>864869</v>
       </c>
       <c r="R37" t="n">
-        <v>7493961</v>
+        <v>7494274</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>

--- a/artfynd/A 34441-2025 artfynd.xlsx
+++ b/artfynd/A 34441-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127497100</v>
+        <v>127497136</v>
       </c>
       <c r="B2" t="n">
-        <v>80025</v>
+        <v>92620</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>864814</v>
+        <v>864673</v>
       </c>
       <c r="R2" t="n">
-        <v>7494119</v>
+        <v>7493901</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127497110</v>
+        <v>127497133</v>
       </c>
       <c r="B3" t="n">
-        <v>80157</v>
+        <v>79018</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>865019</v>
+        <v>865224</v>
       </c>
       <c r="R3" t="n">
-        <v>7494142</v>
+        <v>7494121</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127497136</v>
+        <v>127497134</v>
       </c>
       <c r="B4" t="n">
-        <v>92620</v>
+        <v>79018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>864673</v>
+        <v>865012</v>
       </c>
       <c r="R4" t="n">
-        <v>7493901</v>
+        <v>7493915</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127497133</v>
+        <v>127497100</v>
       </c>
       <c r="B5" t="n">
-        <v>79018</v>
+        <v>80025</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>865224</v>
+        <v>864814</v>
       </c>
       <c r="R5" t="n">
-        <v>7494121</v>
+        <v>7494119</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127497134</v>
+        <v>127497110</v>
       </c>
       <c r="B6" t="n">
-        <v>79018</v>
+        <v>80157</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>865012</v>
+        <v>865019</v>
       </c>
       <c r="R6" t="n">
-        <v>7493915</v>
+        <v>7494142</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>

--- a/artfynd/A 34441-2025 artfynd.xlsx
+++ b/artfynd/A 34441-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127497136</v>
+        <v>127497100</v>
       </c>
       <c r="B2" t="n">
-        <v>92620</v>
+        <v>80027</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>6456</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>864673</v>
+        <v>864814</v>
       </c>
       <c r="R2" t="n">
-        <v>7493901</v>
+        <v>7494119</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127497133</v>
+        <v>127497110</v>
       </c>
       <c r="B3" t="n">
-        <v>79018</v>
+        <v>80159</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>865224</v>
+        <v>865019</v>
       </c>
       <c r="R3" t="n">
-        <v>7494121</v>
+        <v>7494142</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127497134</v>
+        <v>127497133</v>
       </c>
       <c r="B4" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>865012</v>
+        <v>865224</v>
       </c>
       <c r="R4" t="n">
-        <v>7493915</v>
+        <v>7494121</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127497100</v>
+        <v>127497136</v>
       </c>
       <c r="B5" t="n">
-        <v>80025</v>
+        <v>92622</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>864814</v>
+        <v>864673</v>
       </c>
       <c r="R5" t="n">
-        <v>7494119</v>
+        <v>7493901</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127497110</v>
+        <v>127497134</v>
       </c>
       <c r="B6" t="n">
-        <v>80157</v>
+        <v>79020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>865019</v>
+        <v>865012</v>
       </c>
       <c r="R6" t="n">
-        <v>7494142</v>
+        <v>7493915</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1163,7 +1163,7 @@
         <v>127497116</v>
       </c>
       <c r="B7" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127497109</v>
+        <v>127497142</v>
       </c>
       <c r="B8" t="n">
-        <v>80157</v>
+        <v>77998</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6464</v>
+        <v>6487</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>864826</v>
+        <v>864722</v>
       </c>
       <c r="R8" t="n">
-        <v>7494067</v>
+        <v>7493992</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1354,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127497142</v>
+        <v>127497109</v>
       </c>
       <c r="B9" t="n">
-        <v>77996</v>
+        <v>80159</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6487</v>
+        <v>6464</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>864722</v>
+        <v>864826</v>
       </c>
       <c r="R9" t="n">
-        <v>7493992</v>
+        <v>7494067</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1454,7 +1454,7 @@
         <v>127497118</v>
       </c>
       <c r="B10" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127497141</v>
+        <v>127497126</v>
       </c>
       <c r="B11" t="n">
-        <v>92620</v>
+        <v>79020</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>865108</v>
+        <v>865024</v>
       </c>
       <c r="R11" t="n">
-        <v>7493903</v>
+        <v>7494051</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127497126</v>
+        <v>127497141</v>
       </c>
       <c r="B12" t="n">
-        <v>79018</v>
+        <v>92622</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>865024</v>
+        <v>865108</v>
       </c>
       <c r="R12" t="n">
-        <v>7494051</v>
+        <v>7493903</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1745,7 +1745,7 @@
         <v>127497144</v>
       </c>
       <c r="B13" t="n">
-        <v>78424</v>
+        <v>78426</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>127497093</v>
       </c>
       <c r="B14" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>127497111</v>
       </c>
       <c r="B15" t="n">
-        <v>58031</v>
+        <v>58033</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>127497114</v>
       </c>
       <c r="B16" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>127497115</v>
       </c>
       <c r="B17" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>127497117</v>
       </c>
       <c r="B18" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>127497145</v>
       </c>
       <c r="B19" t="n">
-        <v>78424</v>
+        <v>78426</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>127497120</v>
       </c>
       <c r="B20" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>127497107</v>
       </c>
       <c r="B21" t="n">
-        <v>97331</v>
+        <v>97333</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2615,10 +2615,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127497143</v>
+        <v>127497132</v>
       </c>
       <c r="B22" t="n">
-        <v>92614</v>
+        <v>79020</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2626,21 +2626,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4362</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>865176</v>
+        <v>865208</v>
       </c>
       <c r="R22" t="n">
-        <v>7494463</v>
+        <v>7494123</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2712,10 +2712,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127497132</v>
+        <v>127497143</v>
       </c>
       <c r="B23" t="n">
-        <v>79018</v>
+        <v>92616</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2723,21 +2723,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2747,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>865208</v>
+        <v>865176</v>
       </c>
       <c r="R23" t="n">
-        <v>7494123</v>
+        <v>7494463</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2812,7 +2812,7 @@
         <v>127497099</v>
       </c>
       <c r="B24" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>127497130</v>
       </c>
       <c r="B25" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>127497108</v>
       </c>
       <c r="B26" t="n">
-        <v>97331</v>
+        <v>97333</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>127497127</v>
       </c>
       <c r="B27" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>127497137</v>
       </c>
       <c r="B28" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         <v>127497131</v>
       </c>
       <c r="B29" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3394,7 +3394,7 @@
         <v>127497135</v>
       </c>
       <c r="B30" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>127497119</v>
       </c>
       <c r="B31" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>127497129</v>
       </c>
       <c r="B32" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         <v>127497123</v>
       </c>
       <c r="B33" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3779,32 +3779,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127497140</v>
+        <v>127497122</v>
       </c>
       <c r="B34" t="n">
-        <v>92620</v>
+        <v>79020</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3814,10 +3814,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>865254</v>
+        <v>864916</v>
       </c>
       <c r="R34" t="n">
-        <v>7494165</v>
+        <v>7494217</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3876,32 +3876,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127497122</v>
+        <v>127497140</v>
       </c>
       <c r="B35" t="n">
-        <v>79018</v>
+        <v>92622</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3911,10 +3911,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>864916</v>
+        <v>865254</v>
       </c>
       <c r="R35" t="n">
-        <v>7494217</v>
+        <v>7494165</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -3976,7 +3976,7 @@
         <v>127497105</v>
       </c>
       <c r="B36" t="n">
-        <v>97331</v>
+        <v>97333</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>127497106</v>
       </c>
       <c r="B37" t="n">
-        <v>97331</v>
+        <v>97333</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         <v>127497128</v>
       </c>
       <c r="B38" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>127497125</v>
       </c>
       <c r="B39" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>127497124</v>
       </c>
       <c r="B40" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>127497103</v>
       </c>
       <c r="B41" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>127497098</v>
       </c>
       <c r="B42" t="n">
-        <v>91350</v>
+        <v>91352</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4669,7 +4669,7 @@
         <v>127497097</v>
       </c>
       <c r="B43" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         <v>127497096</v>
       </c>
       <c r="B44" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 34441-2025 artfynd.xlsx
+++ b/artfynd/A 34441-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127497100</v>
+        <v>127497133</v>
       </c>
       <c r="B2" t="n">
-        <v>80027</v>
+        <v>79020</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>864814</v>
+        <v>865224</v>
       </c>
       <c r="R2" t="n">
-        <v>7494119</v>
+        <v>7494121</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127497110</v>
+        <v>127497100</v>
       </c>
       <c r="B3" t="n">
-        <v>80159</v>
+        <v>80027</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6464</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>865019</v>
+        <v>864814</v>
       </c>
       <c r="R3" t="n">
-        <v>7494142</v>
+        <v>7494119</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127497133</v>
+        <v>127497134</v>
       </c>
       <c r="B4" t="n">
         <v>79020</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>865224</v>
+        <v>865012</v>
       </c>
       <c r="R4" t="n">
-        <v>7494121</v>
+        <v>7493915</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127497136</v>
+        <v>127497110</v>
       </c>
       <c r="B5" t="n">
-        <v>92622</v>
+        <v>80159</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6464</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>864673</v>
+        <v>865019</v>
       </c>
       <c r="R5" t="n">
-        <v>7493901</v>
+        <v>7494142</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127497134</v>
+        <v>127497136</v>
       </c>
       <c r="B6" t="n">
-        <v>79020</v>
+        <v>92622</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>865012</v>
+        <v>864673</v>
       </c>
       <c r="R6" t="n">
-        <v>7493915</v>
+        <v>7493901</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127497142</v>
+        <v>127497109</v>
       </c>
       <c r="B8" t="n">
-        <v>77998</v>
+        <v>80159</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6487</v>
+        <v>6464</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>864722</v>
+        <v>864826</v>
       </c>
       <c r="R8" t="n">
-        <v>7493992</v>
+        <v>7494067</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1354,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127497109</v>
+        <v>127497142</v>
       </c>
       <c r="B9" t="n">
-        <v>80159</v>
+        <v>77998</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6464</v>
+        <v>6487</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>864826</v>
+        <v>864722</v>
       </c>
       <c r="R9" t="n">
-        <v>7494067</v>
+        <v>7493992</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127497126</v>
+        <v>127497141</v>
       </c>
       <c r="B11" t="n">
-        <v>79020</v>
+        <v>92622</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>865024</v>
+        <v>865108</v>
       </c>
       <c r="R11" t="n">
-        <v>7494051</v>
+        <v>7493903</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127497141</v>
+        <v>127497126</v>
       </c>
       <c r="B12" t="n">
-        <v>92622</v>
+        <v>79020</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>865108</v>
+        <v>865024</v>
       </c>
       <c r="R12" t="n">
-        <v>7493903</v>
+        <v>7494051</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -3197,32 +3197,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127497137</v>
+        <v>127497131</v>
       </c>
       <c r="B28" t="n">
-        <v>92622</v>
+        <v>79020</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3232,10 +3232,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>864714</v>
+        <v>865118</v>
       </c>
       <c r="R28" t="n">
-        <v>7493998</v>
+        <v>7494428</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3294,32 +3294,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127497131</v>
+        <v>127497137</v>
       </c>
       <c r="B29" t="n">
-        <v>79020</v>
+        <v>92622</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3329,10 +3329,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>865118</v>
+        <v>864714</v>
       </c>
       <c r="R29" t="n">
-        <v>7494428</v>
+        <v>7493998</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3779,32 +3779,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127497122</v>
+        <v>127497140</v>
       </c>
       <c r="B34" t="n">
-        <v>79020</v>
+        <v>92622</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3814,10 +3814,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>864916</v>
+        <v>865254</v>
       </c>
       <c r="R34" t="n">
-        <v>7494217</v>
+        <v>7494165</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3876,32 +3876,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127497140</v>
+        <v>127497122</v>
       </c>
       <c r="B35" t="n">
-        <v>92622</v>
+        <v>79020</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3911,10 +3911,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>865254</v>
+        <v>864916</v>
       </c>
       <c r="R35" t="n">
-        <v>7494165</v>
+        <v>7494217</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -3973,7 +3973,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127497105</v>
+        <v>127497106</v>
       </c>
       <c r="B36" t="n">
         <v>97333</v>
@@ -4008,10 +4008,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>864754</v>
+        <v>864869</v>
       </c>
       <c r="R36" t="n">
-        <v>7493961</v>
+        <v>7494274</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4070,7 +4070,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127497106</v>
+        <v>127497105</v>
       </c>
       <c r="B37" t="n">
         <v>97333</v>
@@ -4105,10 +4105,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>864869</v>
+        <v>864754</v>
       </c>
       <c r="R37" t="n">
-        <v>7494274</v>
+        <v>7493961</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4167,7 +4167,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127497128</v>
+        <v>127497125</v>
       </c>
       <c r="B38" t="n">
         <v>79020</v>
@@ -4202,10 +4202,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>864973</v>
+        <v>864993</v>
       </c>
       <c r="R38" t="n">
-        <v>7494288</v>
+        <v>7494054</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4264,7 +4264,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127497125</v>
+        <v>127497128</v>
       </c>
       <c r="B39" t="n">
         <v>79020</v>
@@ -4299,10 +4299,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>864993</v>
+        <v>864973</v>
       </c>
       <c r="R39" t="n">
-        <v>7494054</v>
+        <v>7494288</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>

--- a/artfynd/A 34441-2025 artfynd.xlsx
+++ b/artfynd/A 34441-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127497133</v>
+        <v>127497136</v>
       </c>
       <c r="B2" t="n">
-        <v>79020</v>
+        <v>92622</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>865224</v>
+        <v>864673</v>
       </c>
       <c r="R2" t="n">
-        <v>7494121</v>
+        <v>7493901</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127497136</v>
+        <v>127497133</v>
       </c>
       <c r="B6" t="n">
-        <v>92622</v>
+        <v>79020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>864673</v>
+        <v>865224</v>
       </c>
       <c r="R6" t="n">
-        <v>7493901</v>
+        <v>7494121</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127497141</v>
+        <v>127497126</v>
       </c>
       <c r="B11" t="n">
-        <v>92622</v>
+        <v>79020</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>865108</v>
+        <v>865024</v>
       </c>
       <c r="R11" t="n">
-        <v>7493903</v>
+        <v>7494051</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127497126</v>
+        <v>127497141</v>
       </c>
       <c r="B12" t="n">
-        <v>79020</v>
+        <v>92622</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>865024</v>
+        <v>865108</v>
       </c>
       <c r="R12" t="n">
-        <v>7494051</v>
+        <v>7493903</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2615,10 +2615,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127497132</v>
+        <v>127497099</v>
       </c>
       <c r="B22" t="n">
-        <v>79020</v>
+        <v>57660</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2626,21 +2626,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>865208</v>
+        <v>865213</v>
       </c>
       <c r="R22" t="n">
-        <v>7494123</v>
+        <v>7494422</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2712,10 +2712,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127497143</v>
+        <v>127497132</v>
       </c>
       <c r="B23" t="n">
-        <v>92616</v>
+        <v>79020</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2723,21 +2723,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4362</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2747,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>865176</v>
+        <v>865208</v>
       </c>
       <c r="R23" t="n">
-        <v>7494463</v>
+        <v>7494123</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2809,10 +2809,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127497099</v>
+        <v>127497143</v>
       </c>
       <c r="B24" t="n">
-        <v>57660</v>
+        <v>92616</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2820,21 +2820,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>4362</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>865213</v>
+        <v>865176</v>
       </c>
       <c r="R24" t="n">
-        <v>7494422</v>
+        <v>7494463</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3197,32 +3197,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127497131</v>
+        <v>127497137</v>
       </c>
       <c r="B28" t="n">
-        <v>79020</v>
+        <v>92622</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3232,10 +3232,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>865118</v>
+        <v>864714</v>
       </c>
       <c r="R28" t="n">
-        <v>7494428</v>
+        <v>7493998</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3294,32 +3294,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127497137</v>
+        <v>127497131</v>
       </c>
       <c r="B29" t="n">
-        <v>92622</v>
+        <v>79020</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3329,10 +3329,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>864714</v>
+        <v>865118</v>
       </c>
       <c r="R29" t="n">
-        <v>7493998</v>
+        <v>7494428</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3779,32 +3779,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127497140</v>
+        <v>127497122</v>
       </c>
       <c r="B34" t="n">
-        <v>92622</v>
+        <v>79020</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3814,10 +3814,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>865254</v>
+        <v>864916</v>
       </c>
       <c r="R34" t="n">
-        <v>7494165</v>
+        <v>7494217</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3876,32 +3876,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127497122</v>
+        <v>127497140</v>
       </c>
       <c r="B35" t="n">
-        <v>79020</v>
+        <v>92622</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3911,10 +3911,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>864916</v>
+        <v>865254</v>
       </c>
       <c r="R35" t="n">
-        <v>7494217</v>
+        <v>7494165</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4167,7 +4167,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127497125</v>
+        <v>127497128</v>
       </c>
       <c r="B38" t="n">
         <v>79020</v>
@@ -4202,10 +4202,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>864993</v>
+        <v>864973</v>
       </c>
       <c r="R38" t="n">
-        <v>7494054</v>
+        <v>7494288</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4264,7 +4264,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127497128</v>
+        <v>127497125</v>
       </c>
       <c r="B39" t="n">
         <v>79020</v>
@@ -4299,10 +4299,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>864973</v>
+        <v>864993</v>
       </c>
       <c r="R39" t="n">
-        <v>7494288</v>
+        <v>7494054</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>

--- a/artfynd/A 34441-2025 artfynd.xlsx
+++ b/artfynd/A 34441-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127497136</v>
       </c>
       <c r="B2" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127497100</v>
+        <v>127497133</v>
       </c>
       <c r="B3" t="n">
-        <v>80027</v>
+        <v>79020</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>864814</v>
+        <v>865224</v>
       </c>
       <c r="R3" t="n">
-        <v>7494119</v>
+        <v>7494121</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127497134</v>
+        <v>127497100</v>
       </c>
       <c r="B4" t="n">
-        <v>79020</v>
+        <v>80027</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>865012</v>
+        <v>864814</v>
       </c>
       <c r="R4" t="n">
-        <v>7493915</v>
+        <v>7494119</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127497110</v>
+        <v>127497134</v>
       </c>
       <c r="B5" t="n">
-        <v>80159</v>
+        <v>79020</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>865019</v>
+        <v>865012</v>
       </c>
       <c r="R5" t="n">
-        <v>7494142</v>
+        <v>7493915</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127497133</v>
+        <v>127497110</v>
       </c>
       <c r="B6" t="n">
-        <v>79020</v>
+        <v>80159</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>865224</v>
+        <v>865019</v>
       </c>
       <c r="R6" t="n">
-        <v>7494121</v>
+        <v>7494142</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127497126</v>
+        <v>127497141</v>
       </c>
       <c r="B11" t="n">
-        <v>79020</v>
+        <v>92628</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>865024</v>
+        <v>865108</v>
       </c>
       <c r="R11" t="n">
-        <v>7494051</v>
+        <v>7493903</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127497141</v>
+        <v>127497126</v>
       </c>
       <c r="B12" t="n">
-        <v>92622</v>
+        <v>79020</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>865108</v>
+        <v>865024</v>
       </c>
       <c r="R12" t="n">
-        <v>7493903</v>
+        <v>7494051</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1842,7 +1842,7 @@
         <v>127497093</v>
       </c>
       <c r="B14" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>127497114</v>
       </c>
       <c r="B16" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>127497115</v>
       </c>
       <c r="B17" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>127497107</v>
       </c>
       <c r="B21" t="n">
-        <v>97333</v>
+        <v>97339</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2615,10 +2615,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127497099</v>
+        <v>127497132</v>
       </c>
       <c r="B22" t="n">
-        <v>57660</v>
+        <v>79020</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2626,21 +2626,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>865213</v>
+        <v>865208</v>
       </c>
       <c r="R22" t="n">
-        <v>7494422</v>
+        <v>7494123</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2712,10 +2712,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127497132</v>
+        <v>127497099</v>
       </c>
       <c r="B23" t="n">
-        <v>79020</v>
+        <v>57660</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2723,21 +2723,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2747,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>865208</v>
+        <v>865213</v>
       </c>
       <c r="R23" t="n">
-        <v>7494123</v>
+        <v>7494422</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2812,7 +2812,7 @@
         <v>127497143</v>
       </c>
       <c r="B24" t="n">
-        <v>92616</v>
+        <v>92622</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>127497108</v>
       </c>
       <c r="B26" t="n">
-        <v>97333</v>
+        <v>97339</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>127497137</v>
       </c>
       <c r="B28" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3394,7 +3394,7 @@
         <v>127497135</v>
       </c>
       <c r="B30" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3879,7 +3879,7 @@
         <v>127497140</v>
       </c>
       <c r="B35" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>127497106</v>
       </c>
       <c r="B36" t="n">
-        <v>97333</v>
+        <v>97339</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>127497105</v>
       </c>
       <c r="B37" t="n">
-        <v>97333</v>
+        <v>97339</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4564,10 +4564,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127497098</v>
+        <v>127497097</v>
       </c>
       <c r="B42" t="n">
-        <v>91352</v>
+        <v>57663</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4575,38 +4575,38 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Honkavaara, Nb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>864846</v>
+        <v>865211</v>
       </c>
       <c r="R42" t="n">
-        <v>7494223</v>
+        <v>7494097</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4641,13 +4641,17 @@
           <t>2025-08-13</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4666,10 +4670,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127497097</v>
+        <v>127497098</v>
       </c>
       <c r="B43" t="n">
-        <v>57663</v>
+        <v>91358</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4677,38 +4681,38 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Honkavaara, Nb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>865211</v>
+        <v>864846</v>
       </c>
       <c r="R43" t="n">
-        <v>7494097</v>
+        <v>7494223</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4743,17 +4747,13 @@
           <t>2025-08-13</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 34441-2025 artfynd.xlsx
+++ b/artfynd/A 34441-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127497136</v>
+        <v>127497133</v>
       </c>
       <c r="B2" t="n">
-        <v>92628</v>
+        <v>79023</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>864673</v>
+        <v>865224</v>
       </c>
       <c r="R2" t="n">
-        <v>7493901</v>
+        <v>7494121</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127497133</v>
+        <v>127497136</v>
       </c>
       <c r="B3" t="n">
-        <v>79020</v>
+        <v>92631</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>865224</v>
+        <v>864673</v>
       </c>
       <c r="R3" t="n">
-        <v>7494121</v>
+        <v>7493901</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -872,7 +872,7 @@
         <v>127497100</v>
       </c>
       <c r="B4" t="n">
-        <v>80027</v>
+        <v>80030</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127497134</v>
       </c>
       <c r="B5" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127497110</v>
       </c>
       <c r="B6" t="n">
-        <v>80159</v>
+        <v>80162</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>127497116</v>
       </c>
       <c r="B7" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>127497109</v>
       </c>
       <c r="B8" t="n">
-        <v>80159</v>
+        <v>80162</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>127497142</v>
       </c>
       <c r="B9" t="n">
-        <v>77998</v>
+        <v>78001</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>127497118</v>
       </c>
       <c r="B10" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127497141</v>
+        <v>127497126</v>
       </c>
       <c r="B11" t="n">
-        <v>92628</v>
+        <v>79023</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>865108</v>
+        <v>865024</v>
       </c>
       <c r="R11" t="n">
-        <v>7493903</v>
+        <v>7494051</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127497126</v>
+        <v>127497141</v>
       </c>
       <c r="B12" t="n">
-        <v>79020</v>
+        <v>92631</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>865024</v>
+        <v>865108</v>
       </c>
       <c r="R12" t="n">
-        <v>7494051</v>
+        <v>7493903</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1745,7 +1745,7 @@
         <v>127497144</v>
       </c>
       <c r="B13" t="n">
-        <v>78426</v>
+        <v>78429</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>127497093</v>
       </c>
       <c r="B14" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>127497111</v>
       </c>
       <c r="B15" t="n">
-        <v>58033</v>
+        <v>58036</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>127497114</v>
       </c>
       <c r="B16" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>127497115</v>
       </c>
       <c r="B17" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>127497117</v>
       </c>
       <c r="B18" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>127497145</v>
       </c>
       <c r="B19" t="n">
-        <v>78426</v>
+        <v>78429</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>127497120</v>
       </c>
       <c r="B20" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>127497107</v>
       </c>
       <c r="B21" t="n">
-        <v>97339</v>
+        <v>97342</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2615,10 +2615,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127497132</v>
+        <v>127497143</v>
       </c>
       <c r="B22" t="n">
-        <v>79020</v>
+        <v>92625</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2626,21 +2626,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>865208</v>
+        <v>865176</v>
       </c>
       <c r="R22" t="n">
-        <v>7494123</v>
+        <v>7494463</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2712,10 +2712,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127497099</v>
+        <v>127497132</v>
       </c>
       <c r="B23" t="n">
-        <v>57660</v>
+        <v>79023</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2723,21 +2723,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2747,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>865213</v>
+        <v>865208</v>
       </c>
       <c r="R23" t="n">
-        <v>7494422</v>
+        <v>7494123</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2809,10 +2809,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127497143</v>
+        <v>127497099</v>
       </c>
       <c r="B24" t="n">
-        <v>92622</v>
+        <v>57663</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2820,21 +2820,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4362</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>865176</v>
+        <v>865213</v>
       </c>
       <c r="R24" t="n">
-        <v>7494463</v>
+        <v>7494422</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2909,7 +2909,7 @@
         <v>127497130</v>
       </c>
       <c r="B25" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>127497108</v>
       </c>
       <c r="B26" t="n">
-        <v>97339</v>
+        <v>97342</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>127497127</v>
       </c>
       <c r="B27" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>127497137</v>
       </c>
       <c r="B28" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         <v>127497131</v>
       </c>
       <c r="B29" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3394,7 +3394,7 @@
         <v>127497135</v>
       </c>
       <c r="B30" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>127497119</v>
       </c>
       <c r="B31" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>127497129</v>
       </c>
       <c r="B32" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         <v>127497123</v>
       </c>
       <c r="B33" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>127497122</v>
       </c>
       <c r="B34" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3879,7 +3879,7 @@
         <v>127497140</v>
       </c>
       <c r="B35" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>127497106</v>
       </c>
       <c r="B36" t="n">
-        <v>97339</v>
+        <v>97342</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>127497105</v>
       </c>
       <c r="B37" t="n">
-        <v>97339</v>
+        <v>97342</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4167,10 +4167,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127497128</v>
+        <v>127497125</v>
       </c>
       <c r="B38" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4202,10 +4202,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>864973</v>
+        <v>864993</v>
       </c>
       <c r="R38" t="n">
-        <v>7494288</v>
+        <v>7494054</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4264,10 +4264,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127497125</v>
+        <v>127497124</v>
       </c>
       <c r="B39" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4299,10 +4299,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>864993</v>
+        <v>864971</v>
       </c>
       <c r="R39" t="n">
-        <v>7494054</v>
+        <v>7494087</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4361,10 +4361,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127497124</v>
+        <v>127497128</v>
       </c>
       <c r="B40" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4396,10 +4396,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>864971</v>
+        <v>864973</v>
       </c>
       <c r="R40" t="n">
-        <v>7494087</v>
+        <v>7494288</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4461,7 +4461,7 @@
         <v>127497103</v>
       </c>
       <c r="B41" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4564,10 +4564,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127497097</v>
+        <v>127497098</v>
       </c>
       <c r="B42" t="n">
-        <v>57663</v>
+        <v>91361</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4575,38 +4575,38 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Honkavaara, Nb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>865211</v>
+        <v>864846</v>
       </c>
       <c r="R42" t="n">
-        <v>7494097</v>
+        <v>7494223</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4641,17 +4641,13 @@
           <t>2025-08-13</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4670,10 +4666,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127497098</v>
+        <v>127497097</v>
       </c>
       <c r="B43" t="n">
-        <v>91358</v>
+        <v>57666</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4681,38 +4677,38 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Honkavaara, Nb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>864846</v>
+        <v>865211</v>
       </c>
       <c r="R43" t="n">
-        <v>7494223</v>
+        <v>7494097</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4747,13 +4743,17 @@
           <t>2025-08-13</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4775,7 +4775,7 @@
         <v>127497096</v>
       </c>
       <c r="B44" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 34441-2025 artfynd.xlsx
+++ b/artfynd/A 34441-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127497133</v>
       </c>
       <c r="B2" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127497136</v>
+        <v>127497100</v>
       </c>
       <c r="B3" t="n">
-        <v>92631</v>
+        <v>80036</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>864673</v>
+        <v>864814</v>
       </c>
       <c r="R3" t="n">
-        <v>7493901</v>
+        <v>7494119</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127497100</v>
+        <v>127497134</v>
       </c>
       <c r="B4" t="n">
-        <v>80030</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>864814</v>
+        <v>865012</v>
       </c>
       <c r="R4" t="n">
-        <v>7494119</v>
+        <v>7493915</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127497134</v>
+        <v>127497110</v>
       </c>
       <c r="B5" t="n">
-        <v>79023</v>
+        <v>80168</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>865012</v>
+        <v>865019</v>
       </c>
       <c r="R5" t="n">
-        <v>7493915</v>
+        <v>7494142</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127497110</v>
+        <v>127497136</v>
       </c>
       <c r="B6" t="n">
-        <v>80162</v>
+        <v>92639</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6464</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>865019</v>
+        <v>864673</v>
       </c>
       <c r="R6" t="n">
-        <v>7494142</v>
+        <v>7493901</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1163,7 +1163,7 @@
         <v>127497116</v>
       </c>
       <c r="B7" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>127497109</v>
       </c>
       <c r="B8" t="n">
-        <v>80162</v>
+        <v>80168</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>127497142</v>
       </c>
       <c r="B9" t="n">
-        <v>78001</v>
+        <v>78007</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>127497118</v>
       </c>
       <c r="B10" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>127497126</v>
       </c>
       <c r="B11" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127497141</v>
+        <v>127497144</v>
       </c>
       <c r="B12" t="n">
-        <v>92631</v>
+        <v>78435</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>865108</v>
+        <v>864722</v>
       </c>
       <c r="R12" t="n">
-        <v>7493903</v>
+        <v>7493995</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1742,32 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127497144</v>
+        <v>127497141</v>
       </c>
       <c r="B13" t="n">
-        <v>78429</v>
+        <v>92639</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>864722</v>
+        <v>865108</v>
       </c>
       <c r="R13" t="n">
-        <v>7493995</v>
+        <v>7493903</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1842,7 +1842,7 @@
         <v>127497093</v>
       </c>
       <c r="B14" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>127497111</v>
       </c>
       <c r="B15" t="n">
-        <v>58036</v>
+        <v>58042</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>127497114</v>
       </c>
       <c r="B16" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>127497115</v>
       </c>
       <c r="B17" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>127497117</v>
       </c>
       <c r="B18" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>127497145</v>
       </c>
       <c r="B19" t="n">
-        <v>78429</v>
+        <v>78435</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>127497120</v>
       </c>
       <c r="B20" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>127497107</v>
       </c>
       <c r="B21" t="n">
-        <v>97342</v>
+        <v>97350</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2615,10 +2615,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127497143</v>
+        <v>127497132</v>
       </c>
       <c r="B22" t="n">
-        <v>92625</v>
+        <v>79029</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2626,21 +2626,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4362</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>865176</v>
+        <v>865208</v>
       </c>
       <c r="R22" t="n">
-        <v>7494463</v>
+        <v>7494123</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2712,10 +2712,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127497132</v>
+        <v>127497143</v>
       </c>
       <c r="B23" t="n">
-        <v>79023</v>
+        <v>92633</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2723,21 +2723,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2747,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>865208</v>
+        <v>865176</v>
       </c>
       <c r="R23" t="n">
-        <v>7494123</v>
+        <v>7494463</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2812,7 +2812,7 @@
         <v>127497099</v>
       </c>
       <c r="B24" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>127497130</v>
       </c>
       <c r="B25" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>127497108</v>
       </c>
       <c r="B26" t="n">
-        <v>97342</v>
+        <v>97350</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>127497127</v>
       </c>
       <c r="B27" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3197,32 +3197,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127497137</v>
+        <v>127497131</v>
       </c>
       <c r="B28" t="n">
-        <v>92631</v>
+        <v>79029</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3232,10 +3232,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>864714</v>
+        <v>865118</v>
       </c>
       <c r="R28" t="n">
-        <v>7493998</v>
+        <v>7494428</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3294,32 +3294,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127497131</v>
+        <v>127497137</v>
       </c>
       <c r="B29" t="n">
-        <v>79023</v>
+        <v>92639</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3329,10 +3329,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>865118</v>
+        <v>864714</v>
       </c>
       <c r="R29" t="n">
-        <v>7494428</v>
+        <v>7493998</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3391,32 +3391,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127497135</v>
+        <v>127497119</v>
       </c>
       <c r="B30" t="n">
-        <v>92631</v>
+        <v>79029</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3426,10 +3426,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>864717</v>
+        <v>864839</v>
       </c>
       <c r="R30" t="n">
-        <v>7493817</v>
+        <v>7494049</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3488,32 +3488,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127497119</v>
+        <v>127497135</v>
       </c>
       <c r="B31" t="n">
-        <v>79023</v>
+        <v>92639</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3523,10 +3523,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>864839</v>
+        <v>864717</v>
       </c>
       <c r="R31" t="n">
-        <v>7494049</v>
+        <v>7493817</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3588,7 +3588,7 @@
         <v>127497129</v>
       </c>
       <c r="B32" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         <v>127497123</v>
       </c>
       <c r="B33" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>127497122</v>
       </c>
       <c r="B34" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3879,7 +3879,7 @@
         <v>127497140</v>
       </c>
       <c r="B35" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>127497106</v>
       </c>
       <c r="B36" t="n">
-        <v>97342</v>
+        <v>97350</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>127497105</v>
       </c>
       <c r="B37" t="n">
-        <v>97342</v>
+        <v>97350</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4167,10 +4167,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127497125</v>
+        <v>127497128</v>
       </c>
       <c r="B38" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4202,10 +4202,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>864993</v>
+        <v>864973</v>
       </c>
       <c r="R38" t="n">
-        <v>7494054</v>
+        <v>7494288</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4264,10 +4264,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127497124</v>
+        <v>127497125</v>
       </c>
       <c r="B39" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4299,10 +4299,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>864971</v>
+        <v>864993</v>
       </c>
       <c r="R39" t="n">
-        <v>7494087</v>
+        <v>7494054</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4361,10 +4361,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127497128</v>
+        <v>127497124</v>
       </c>
       <c r="B40" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4396,10 +4396,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>864973</v>
+        <v>864971</v>
       </c>
       <c r="R40" t="n">
-        <v>7494288</v>
+        <v>7494087</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4461,7 +4461,7 @@
         <v>127497103</v>
       </c>
       <c r="B41" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4564,10 +4564,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127497098</v>
+        <v>127497097</v>
       </c>
       <c r="B42" t="n">
-        <v>91361</v>
+        <v>57672</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4575,38 +4575,38 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Honkavaara, Nb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>864846</v>
+        <v>865211</v>
       </c>
       <c r="R42" t="n">
-        <v>7494223</v>
+        <v>7494097</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4641,13 +4641,17 @@
           <t>2025-08-13</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4666,10 +4670,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127497097</v>
+        <v>127497098</v>
       </c>
       <c r="B43" t="n">
-        <v>57666</v>
+        <v>91369</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4677,38 +4681,38 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Honkavaara, Nb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>865211</v>
+        <v>864846</v>
       </c>
       <c r="R43" t="n">
-        <v>7494097</v>
+        <v>7494223</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4743,17 +4747,13 @@
           <t>2025-08-13</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4775,7 +4775,7 @@
         <v>127497096</v>
       </c>
       <c r="B44" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 34441-2025 artfynd.xlsx
+++ b/artfynd/A 34441-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127497133</v>
+        <v>127497136</v>
       </c>
       <c r="B2" t="n">
-        <v>79029</v>
+        <v>92640</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>865224</v>
+        <v>864673</v>
       </c>
       <c r="R2" t="n">
-        <v>7494121</v>
+        <v>7493901</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127497100</v>
+        <v>127497133</v>
       </c>
       <c r="B3" t="n">
-        <v>80036</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>864814</v>
+        <v>865224</v>
       </c>
       <c r="R3" t="n">
-        <v>7494119</v>
+        <v>7494121</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127497134</v>
+        <v>127497100</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>80036</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>865012</v>
+        <v>864814</v>
       </c>
       <c r="R4" t="n">
-        <v>7493915</v>
+        <v>7494119</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127497110</v>
+        <v>127497134</v>
       </c>
       <c r="B5" t="n">
-        <v>80168</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>865019</v>
+        <v>865012</v>
       </c>
       <c r="R5" t="n">
-        <v>7494142</v>
+        <v>7493915</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127497136</v>
+        <v>127497110</v>
       </c>
       <c r="B6" t="n">
-        <v>92639</v>
+        <v>80168</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>6464</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>864673</v>
+        <v>865019</v>
       </c>
       <c r="R6" t="n">
-        <v>7493901</v>
+        <v>7494142</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127497109</v>
+        <v>127497142</v>
       </c>
       <c r="B8" t="n">
-        <v>80168</v>
+        <v>78007</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6464</v>
+        <v>6487</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>864826</v>
+        <v>864722</v>
       </c>
       <c r="R8" t="n">
-        <v>7494067</v>
+        <v>7493992</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1354,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127497142</v>
+        <v>127497109</v>
       </c>
       <c r="B9" t="n">
-        <v>78007</v>
+        <v>80168</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6487</v>
+        <v>6464</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>864722</v>
+        <v>864826</v>
       </c>
       <c r="R9" t="n">
-        <v>7493992</v>
+        <v>7494067</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127497126</v>
+        <v>127497144</v>
       </c>
       <c r="B11" t="n">
-        <v>79029</v>
+        <v>78435</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>865024</v>
+        <v>864722</v>
       </c>
       <c r="R11" t="n">
-        <v>7494051</v>
+        <v>7493995</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1645,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127497144</v>
+        <v>127497126</v>
       </c>
       <c r="B12" t="n">
-        <v>78435</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>864722</v>
+        <v>865024</v>
       </c>
       <c r="R12" t="n">
-        <v>7493995</v>
+        <v>7494051</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1745,7 +1745,7 @@
         <v>127497141</v>
       </c>
       <c r="B13" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>127497093</v>
       </c>
       <c r="B14" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>127497114</v>
       </c>
       <c r="B16" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>127497115</v>
       </c>
       <c r="B17" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>127497107</v>
       </c>
       <c r="B21" t="n">
-        <v>97350</v>
+        <v>97351</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2615,10 +2615,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127497132</v>
+        <v>127497099</v>
       </c>
       <c r="B22" t="n">
-        <v>79029</v>
+        <v>57669</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2626,21 +2626,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>865208</v>
+        <v>865213</v>
       </c>
       <c r="R22" t="n">
-        <v>7494123</v>
+        <v>7494422</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2712,10 +2712,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127497143</v>
+        <v>127497132</v>
       </c>
       <c r="B23" t="n">
-        <v>92633</v>
+        <v>79029</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2723,21 +2723,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4362</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2747,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>865176</v>
+        <v>865208</v>
       </c>
       <c r="R23" t="n">
-        <v>7494463</v>
+        <v>7494123</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2809,10 +2809,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127497099</v>
+        <v>127497143</v>
       </c>
       <c r="B24" t="n">
-        <v>57669</v>
+        <v>92634</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2820,21 +2820,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>4362</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>865213</v>
+        <v>865176</v>
       </c>
       <c r="R24" t="n">
-        <v>7494422</v>
+        <v>7494463</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3006,7 +3006,7 @@
         <v>127497108</v>
       </c>
       <c r="B26" t="n">
-        <v>97350</v>
+        <v>97351</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3197,32 +3197,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127497131</v>
+        <v>127497137</v>
       </c>
       <c r="B28" t="n">
-        <v>79029</v>
+        <v>92640</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3232,10 +3232,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>865118</v>
+        <v>864714</v>
       </c>
       <c r="R28" t="n">
-        <v>7494428</v>
+        <v>7493998</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3294,32 +3294,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127497137</v>
+        <v>127497131</v>
       </c>
       <c r="B29" t="n">
-        <v>92639</v>
+        <v>79029</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3329,10 +3329,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>864714</v>
+        <v>865118</v>
       </c>
       <c r="R29" t="n">
-        <v>7493998</v>
+        <v>7494428</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3491,7 +3491,7 @@
         <v>127497135</v>
       </c>
       <c r="B31" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3879,7 +3879,7 @@
         <v>127497140</v>
       </c>
       <c r="B35" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>127497106</v>
       </c>
       <c r="B36" t="n">
-        <v>97350</v>
+        <v>97351</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>127497105</v>
       </c>
       <c r="B37" t="n">
-        <v>97350</v>
+        <v>97351</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4564,10 +4564,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127497097</v>
+        <v>127497098</v>
       </c>
       <c r="B42" t="n">
-        <v>57672</v>
+        <v>91370</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4575,38 +4575,38 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Honkavaara, Nb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>865211</v>
+        <v>864846</v>
       </c>
       <c r="R42" t="n">
-        <v>7494097</v>
+        <v>7494223</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4641,17 +4641,13 @@
           <t>2025-08-13</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4670,10 +4666,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127497098</v>
+        <v>127497097</v>
       </c>
       <c r="B43" t="n">
-        <v>91369</v>
+        <v>57672</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4681,38 +4677,38 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Honkavaara, Nb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>864846</v>
+        <v>865211</v>
       </c>
       <c r="R43" t="n">
-        <v>7494223</v>
+        <v>7494097</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4747,13 +4743,17 @@
           <t>2025-08-13</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 34441-2025 artfynd.xlsx
+++ b/artfynd/A 34441-2025 artfynd.xlsx
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127497142</v>
+        <v>127497109</v>
       </c>
       <c r="B8" t="n">
-        <v>78007</v>
+        <v>80168</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6487</v>
+        <v>6464</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>864722</v>
+        <v>864826</v>
       </c>
       <c r="R8" t="n">
-        <v>7493992</v>
+        <v>7494067</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1354,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127497109</v>
+        <v>127497142</v>
       </c>
       <c r="B9" t="n">
-        <v>80168</v>
+        <v>78007</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6464</v>
+        <v>6487</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>864826</v>
+        <v>864722</v>
       </c>
       <c r="R9" t="n">
-        <v>7494067</v>
+        <v>7493992</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127497144</v>
+        <v>127497126</v>
       </c>
       <c r="B11" t="n">
-        <v>78435</v>
+        <v>79029</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>864722</v>
+        <v>865024</v>
       </c>
       <c r="R11" t="n">
-        <v>7493995</v>
+        <v>7494051</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127497126</v>
+        <v>127497141</v>
       </c>
       <c r="B12" t="n">
-        <v>79029</v>
+        <v>92640</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>865024</v>
+        <v>865108</v>
       </c>
       <c r="R12" t="n">
-        <v>7494051</v>
+        <v>7493903</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1742,32 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127497141</v>
+        <v>127497144</v>
       </c>
       <c r="B13" t="n">
-        <v>92640</v>
+        <v>78435</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>865108</v>
+        <v>864722</v>
       </c>
       <c r="R13" t="n">
-        <v>7493903</v>
+        <v>7493995</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2033,7 +2033,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127497114</v>
+        <v>127497115</v>
       </c>
       <c r="B16" t="n">
         <v>91368</v>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>865027</v>
+        <v>865088</v>
       </c>
       <c r="R16" t="n">
-        <v>7494163</v>
+        <v>7494361</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2130,7 +2130,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127497115</v>
+        <v>127497114</v>
       </c>
       <c r="B17" t="n">
         <v>91368</v>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>865088</v>
+        <v>865027</v>
       </c>
       <c r="R17" t="n">
-        <v>7494361</v>
+        <v>7494163</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2615,10 +2615,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127497099</v>
+        <v>127497143</v>
       </c>
       <c r="B22" t="n">
-        <v>57669</v>
+        <v>92634</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2626,21 +2626,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>4362</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>865213</v>
+        <v>865176</v>
       </c>
       <c r="R22" t="n">
-        <v>7494422</v>
+        <v>7494463</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2712,10 +2712,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127497132</v>
+        <v>127497099</v>
       </c>
       <c r="B23" t="n">
-        <v>79029</v>
+        <v>57669</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2723,21 +2723,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2747,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>865208</v>
+        <v>865213</v>
       </c>
       <c r="R23" t="n">
-        <v>7494123</v>
+        <v>7494422</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2809,10 +2809,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127497143</v>
+        <v>127497132</v>
       </c>
       <c r="B24" t="n">
-        <v>92634</v>
+        <v>79029</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2820,21 +2820,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4362</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>865176</v>
+        <v>865208</v>
       </c>
       <c r="R24" t="n">
-        <v>7494463</v>
+        <v>7494123</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3391,32 +3391,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127497119</v>
+        <v>127497135</v>
       </c>
       <c r="B30" t="n">
-        <v>79029</v>
+        <v>92640</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3426,10 +3426,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>864839</v>
+        <v>864717</v>
       </c>
       <c r="R30" t="n">
-        <v>7494049</v>
+        <v>7493817</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3488,32 +3488,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127497135</v>
+        <v>127497119</v>
       </c>
       <c r="B31" t="n">
-        <v>92640</v>
+        <v>79029</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3523,10 +3523,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>864717</v>
+        <v>864839</v>
       </c>
       <c r="R31" t="n">
-        <v>7493817</v>
+        <v>7494049</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3779,32 +3779,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127497122</v>
+        <v>127497140</v>
       </c>
       <c r="B34" t="n">
-        <v>79029</v>
+        <v>92640</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3814,10 +3814,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>864916</v>
+        <v>865254</v>
       </c>
       <c r="R34" t="n">
-        <v>7494217</v>
+        <v>7494165</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3876,32 +3876,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127497140</v>
+        <v>127497122</v>
       </c>
       <c r="B35" t="n">
-        <v>92640</v>
+        <v>79029</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3911,10 +3911,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>865254</v>
+        <v>864916</v>
       </c>
       <c r="R35" t="n">
-        <v>7494165</v>
+        <v>7494217</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>

--- a/artfynd/A 34441-2025 artfynd.xlsx
+++ b/artfynd/A 34441-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127497136</v>
+        <v>127497133</v>
       </c>
       <c r="B2" t="n">
-        <v>92640</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>864673</v>
+        <v>865224</v>
       </c>
       <c r="R2" t="n">
-        <v>7493901</v>
+        <v>7494121</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127497133</v>
+        <v>127497136</v>
       </c>
       <c r="B3" t="n">
-        <v>79029</v>
+        <v>92641</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>865224</v>
+        <v>864673</v>
       </c>
       <c r="R3" t="n">
-        <v>7494121</v>
+        <v>7493901</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127497109</v>
+        <v>127497118</v>
       </c>
       <c r="B8" t="n">
-        <v>80168</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>864826</v>
+        <v>864875</v>
       </c>
       <c r="R8" t="n">
-        <v>7494067</v>
+        <v>7493981</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1354,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127497142</v>
+        <v>127497109</v>
       </c>
       <c r="B9" t="n">
-        <v>78007</v>
+        <v>80168</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6487</v>
+        <v>6464</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>864722</v>
+        <v>864826</v>
       </c>
       <c r="R9" t="n">
-        <v>7493992</v>
+        <v>7494067</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127497118</v>
+        <v>127497142</v>
       </c>
       <c r="B10" t="n">
-        <v>79029</v>
+        <v>78007</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>864875</v>
+        <v>864722</v>
       </c>
       <c r="R10" t="n">
-        <v>7493981</v>
+        <v>7493992</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1648,7 +1648,7 @@
         <v>127497141</v>
       </c>
       <c r="B12" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>127497093</v>
       </c>
       <c r="B14" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127497115</v>
+        <v>127497114</v>
       </c>
       <c r="B16" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>865088</v>
+        <v>865027</v>
       </c>
       <c r="R16" t="n">
-        <v>7494361</v>
+        <v>7494163</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127497114</v>
+        <v>127497115</v>
       </c>
       <c r="B17" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>865027</v>
+        <v>865088</v>
       </c>
       <c r="R17" t="n">
-        <v>7494163</v>
+        <v>7494361</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2521,7 +2521,7 @@
         <v>127497107</v>
       </c>
       <c r="B21" t="n">
-        <v>97351</v>
+        <v>97352</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2615,10 +2615,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127497143</v>
+        <v>127497132</v>
       </c>
       <c r="B22" t="n">
-        <v>92634</v>
+        <v>79029</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2626,21 +2626,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4362</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>865176</v>
+        <v>865208</v>
       </c>
       <c r="R22" t="n">
-        <v>7494463</v>
+        <v>7494123</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2712,10 +2712,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127497099</v>
+        <v>127497143</v>
       </c>
       <c r="B23" t="n">
-        <v>57669</v>
+        <v>92635</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2723,21 +2723,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>4362</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2747,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>865213</v>
+        <v>865176</v>
       </c>
       <c r="R23" t="n">
-        <v>7494422</v>
+        <v>7494463</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2809,10 +2809,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127497132</v>
+        <v>127497099</v>
       </c>
       <c r="B24" t="n">
-        <v>79029</v>
+        <v>57669</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2820,21 +2820,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>865208</v>
+        <v>865213</v>
       </c>
       <c r="R24" t="n">
-        <v>7494123</v>
+        <v>7494422</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3006,7 +3006,7 @@
         <v>127497108</v>
       </c>
       <c r="B26" t="n">
-        <v>97351</v>
+        <v>97352</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>127497137</v>
       </c>
       <c r="B28" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3391,32 +3391,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127497135</v>
+        <v>127497119</v>
       </c>
       <c r="B30" t="n">
-        <v>92640</v>
+        <v>79029</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3426,10 +3426,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>864717</v>
+        <v>864839</v>
       </c>
       <c r="R30" t="n">
-        <v>7493817</v>
+        <v>7494049</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3488,32 +3488,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127497119</v>
+        <v>127497135</v>
       </c>
       <c r="B31" t="n">
-        <v>79029</v>
+        <v>92641</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3523,10 +3523,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>864839</v>
+        <v>864717</v>
       </c>
       <c r="R31" t="n">
-        <v>7494049</v>
+        <v>7493817</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3782,7 +3782,7 @@
         <v>127497140</v>
       </c>
       <c r="B34" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>127497106</v>
       </c>
       <c r="B36" t="n">
-        <v>97351</v>
+        <v>97352</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>127497105</v>
       </c>
       <c r="B37" t="n">
-        <v>97351</v>
+        <v>97352</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>127497098</v>
       </c>
       <c r="B42" t="n">
-        <v>91370</v>
+        <v>91371</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 34441-2025 artfynd.xlsx
+++ b/artfynd/A 34441-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127497136</v>
+        <v>127497100</v>
       </c>
       <c r="B3" t="n">
-        <v>92641</v>
+        <v>80036</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>864673</v>
+        <v>864814</v>
       </c>
       <c r="R3" t="n">
-        <v>7493901</v>
+        <v>7494119</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127497100</v>
+        <v>127497134</v>
       </c>
       <c r="B4" t="n">
-        <v>80036</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>864814</v>
+        <v>865012</v>
       </c>
       <c r="R4" t="n">
-        <v>7494119</v>
+        <v>7493915</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127497134</v>
+        <v>127497110</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>80168</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>865012</v>
+        <v>865019</v>
       </c>
       <c r="R5" t="n">
-        <v>7493915</v>
+        <v>7494142</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127497110</v>
+        <v>127497136</v>
       </c>
       <c r="B6" t="n">
-        <v>80168</v>
+        <v>92642</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6464</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>865019</v>
+        <v>864673</v>
       </c>
       <c r="R6" t="n">
-        <v>7494142</v>
+        <v>7493901</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127497118</v>
+        <v>127497109</v>
       </c>
       <c r="B8" t="n">
-        <v>79029</v>
+        <v>80168</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>864875</v>
+        <v>864826</v>
       </c>
       <c r="R8" t="n">
-        <v>7493981</v>
+        <v>7494067</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1354,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127497109</v>
+        <v>127497142</v>
       </c>
       <c r="B9" t="n">
-        <v>80168</v>
+        <v>78007</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6464</v>
+        <v>6487</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>864826</v>
+        <v>864722</v>
       </c>
       <c r="R9" t="n">
-        <v>7494067</v>
+        <v>7493992</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127497142</v>
+        <v>127497118</v>
       </c>
       <c r="B10" t="n">
-        <v>78007</v>
+        <v>79029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>864722</v>
+        <v>864875</v>
       </c>
       <c r="R10" t="n">
-        <v>7493992</v>
+        <v>7493981</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127497126</v>
+        <v>127497141</v>
       </c>
       <c r="B11" t="n">
-        <v>79029</v>
+        <v>92642</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>865024</v>
+        <v>865108</v>
       </c>
       <c r="R11" t="n">
-        <v>7494051</v>
+        <v>7493903</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127497141</v>
+        <v>127497126</v>
       </c>
       <c r="B12" t="n">
-        <v>92641</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>865108</v>
+        <v>865024</v>
       </c>
       <c r="R12" t="n">
-        <v>7493903</v>
+        <v>7494051</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1842,7 +1842,7 @@
         <v>127497093</v>
       </c>
       <c r="B14" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>127497114</v>
       </c>
       <c r="B16" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>127497115</v>
       </c>
       <c r="B17" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>127497107</v>
       </c>
       <c r="B21" t="n">
-        <v>97352</v>
+        <v>97353</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>127497143</v>
       </c>
       <c r="B23" t="n">
-        <v>92635</v>
+        <v>92636</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>127497108</v>
       </c>
       <c r="B26" t="n">
-        <v>97352</v>
+        <v>97353</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3197,32 +3197,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127497137</v>
+        <v>127497131</v>
       </c>
       <c r="B28" t="n">
-        <v>92641</v>
+        <v>79029</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3232,10 +3232,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>864714</v>
+        <v>865118</v>
       </c>
       <c r="R28" t="n">
-        <v>7493998</v>
+        <v>7494428</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3294,32 +3294,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127497131</v>
+        <v>127497137</v>
       </c>
       <c r="B29" t="n">
-        <v>79029</v>
+        <v>92642</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3329,10 +3329,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>865118</v>
+        <v>864714</v>
       </c>
       <c r="R29" t="n">
-        <v>7494428</v>
+        <v>7493998</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3491,7 +3491,7 @@
         <v>127497135</v>
       </c>
       <c r="B31" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3779,32 +3779,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127497140</v>
+        <v>127497122</v>
       </c>
       <c r="B34" t="n">
-        <v>92641</v>
+        <v>79029</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3814,10 +3814,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>865254</v>
+        <v>864916</v>
       </c>
       <c r="R34" t="n">
-        <v>7494165</v>
+        <v>7494217</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3876,32 +3876,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127497122</v>
+        <v>127497140</v>
       </c>
       <c r="B35" t="n">
-        <v>79029</v>
+        <v>92642</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3911,10 +3911,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>864916</v>
+        <v>865254</v>
       </c>
       <c r="R35" t="n">
-        <v>7494217</v>
+        <v>7494165</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -3976,7 +3976,7 @@
         <v>127497106</v>
       </c>
       <c r="B36" t="n">
-        <v>97352</v>
+        <v>97353</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>127497105</v>
       </c>
       <c r="B37" t="n">
-        <v>97352</v>
+        <v>97353</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>127497098</v>
       </c>
       <c r="B42" t="n">
-        <v>91371</v>
+        <v>91372</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 34441-2025 artfynd.xlsx
+++ b/artfynd/A 34441-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127497100</v>
+        <v>127497136</v>
       </c>
       <c r="B3" t="n">
-        <v>80036</v>
+        <v>92642</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>864814</v>
+        <v>864673</v>
       </c>
       <c r="R3" t="n">
-        <v>7494119</v>
+        <v>7493901</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127497134</v>
+        <v>127497100</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>80036</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>865012</v>
+        <v>864814</v>
       </c>
       <c r="R4" t="n">
-        <v>7493915</v>
+        <v>7494119</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127497136</v>
+        <v>127497134</v>
       </c>
       <c r="B6" t="n">
-        <v>92642</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>864673</v>
+        <v>865012</v>
       </c>
       <c r="R6" t="n">
-        <v>7493901</v>
+        <v>7493915</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127497109</v>
+        <v>127497118</v>
       </c>
       <c r="B8" t="n">
-        <v>80168</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>864826</v>
+        <v>864875</v>
       </c>
       <c r="R8" t="n">
-        <v>7494067</v>
+        <v>7493981</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1354,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127497142</v>
+        <v>127497109</v>
       </c>
       <c r="B9" t="n">
-        <v>78007</v>
+        <v>80168</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6487</v>
+        <v>6464</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>864722</v>
+        <v>864826</v>
       </c>
       <c r="R9" t="n">
-        <v>7493992</v>
+        <v>7494067</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127497118</v>
+        <v>127497142</v>
       </c>
       <c r="B10" t="n">
-        <v>79029</v>
+        <v>78007</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>864875</v>
+        <v>864722</v>
       </c>
       <c r="R10" t="n">
-        <v>7493981</v>
+        <v>7493992</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127497141</v>
+        <v>127497126</v>
       </c>
       <c r="B11" t="n">
-        <v>92642</v>
+        <v>79029</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>865108</v>
+        <v>865024</v>
       </c>
       <c r="R11" t="n">
-        <v>7493903</v>
+        <v>7494051</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127497126</v>
+        <v>127497141</v>
       </c>
       <c r="B12" t="n">
-        <v>79029</v>
+        <v>92642</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>865024</v>
+        <v>865108</v>
       </c>
       <c r="R12" t="n">
-        <v>7494051</v>
+        <v>7493903</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127497145</v>
+        <v>127497120</v>
       </c>
       <c r="B19" t="n">
-        <v>78435</v>
+        <v>79029</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2335,21 +2335,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>865232</v>
+        <v>864828</v>
       </c>
       <c r="R19" t="n">
-        <v>7494161</v>
+        <v>7494091</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2421,10 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127497120</v>
+        <v>127497145</v>
       </c>
       <c r="B20" t="n">
-        <v>79029</v>
+        <v>78435</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2432,21 +2432,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>864828</v>
+        <v>865232</v>
       </c>
       <c r="R20" t="n">
-        <v>7494091</v>
+        <v>7494161</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2615,10 +2615,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127497132</v>
+        <v>127497099</v>
       </c>
       <c r="B22" t="n">
-        <v>79029</v>
+        <v>57669</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2626,21 +2626,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>865208</v>
+        <v>865213</v>
       </c>
       <c r="R22" t="n">
-        <v>7494123</v>
+        <v>7494422</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2712,10 +2712,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127497143</v>
+        <v>127497132</v>
       </c>
       <c r="B23" t="n">
-        <v>92636</v>
+        <v>79029</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2723,21 +2723,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4362</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2747,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>865176</v>
+        <v>865208</v>
       </c>
       <c r="R23" t="n">
-        <v>7494463</v>
+        <v>7494123</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2809,10 +2809,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127497099</v>
+        <v>127497143</v>
       </c>
       <c r="B24" t="n">
-        <v>57669</v>
+        <v>92636</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2820,21 +2820,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>4362</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>865213</v>
+        <v>865176</v>
       </c>
       <c r="R24" t="n">
-        <v>7494422</v>
+        <v>7494463</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3197,32 +3197,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127497131</v>
+        <v>127497137</v>
       </c>
       <c r="B28" t="n">
-        <v>79029</v>
+        <v>92642</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3232,10 +3232,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>865118</v>
+        <v>864714</v>
       </c>
       <c r="R28" t="n">
-        <v>7494428</v>
+        <v>7493998</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3294,32 +3294,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127497137</v>
+        <v>127497131</v>
       </c>
       <c r="B29" t="n">
-        <v>92642</v>
+        <v>79029</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3329,10 +3329,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>864714</v>
+        <v>865118</v>
       </c>
       <c r="R29" t="n">
-        <v>7493998</v>
+        <v>7494428</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3779,32 +3779,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127497122</v>
+        <v>127497140</v>
       </c>
       <c r="B34" t="n">
-        <v>79029</v>
+        <v>92642</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3814,10 +3814,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>864916</v>
+        <v>865254</v>
       </c>
       <c r="R34" t="n">
-        <v>7494217</v>
+        <v>7494165</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3876,32 +3876,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127497140</v>
+        <v>127497122</v>
       </c>
       <c r="B35" t="n">
-        <v>92642</v>
+        <v>79029</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3911,10 +3911,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>865254</v>
+        <v>864916</v>
       </c>
       <c r="R35" t="n">
-        <v>7494165</v>
+        <v>7494217</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4264,7 +4264,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127497125</v>
+        <v>127497124</v>
       </c>
       <c r="B39" t="n">
         <v>79029</v>
@@ -4299,10 +4299,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>864993</v>
+        <v>864971</v>
       </c>
       <c r="R39" t="n">
-        <v>7494054</v>
+        <v>7494087</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4361,7 +4361,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127497124</v>
+        <v>127497125</v>
       </c>
       <c r="B40" t="n">
         <v>79029</v>
@@ -4396,10 +4396,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>864971</v>
+        <v>864993</v>
       </c>
       <c r="R40" t="n">
-        <v>7494087</v>
+        <v>7494054</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>

--- a/artfynd/A 34441-2025 artfynd.xlsx
+++ b/artfynd/A 34441-2025 artfynd.xlsx
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127497100</v>
+        <v>127497134</v>
       </c>
       <c r="B4" t="n">
-        <v>80036</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>864814</v>
+        <v>865012</v>
       </c>
       <c r="R4" t="n">
-        <v>7494119</v>
+        <v>7493915</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127497110</v>
+        <v>127497100</v>
       </c>
       <c r="B5" t="n">
-        <v>80168</v>
+        <v>80036</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>6456</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>865019</v>
+        <v>864814</v>
       </c>
       <c r="R5" t="n">
-        <v>7494142</v>
+        <v>7494119</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127497134</v>
+        <v>127497110</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>80168</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>865012</v>
+        <v>865019</v>
       </c>
       <c r="R6" t="n">
-        <v>7493915</v>
+        <v>7494142</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>

--- a/artfynd/A 34441-2025 artfynd.xlsx
+++ b/artfynd/A 34441-2025 artfynd.xlsx
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127497134</v>
+        <v>127497100</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>80036</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>865012</v>
+        <v>864814</v>
       </c>
       <c r="R4" t="n">
-        <v>7493915</v>
+        <v>7494119</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127497100</v>
+        <v>127497110</v>
       </c>
       <c r="B5" t="n">
-        <v>80036</v>
+        <v>80168</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>6464</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>864814</v>
+        <v>865019</v>
       </c>
       <c r="R5" t="n">
-        <v>7494119</v>
+        <v>7494142</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127497110</v>
+        <v>127497134</v>
       </c>
       <c r="B6" t="n">
-        <v>80168</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>865019</v>
+        <v>865012</v>
       </c>
       <c r="R6" t="n">
-        <v>7494142</v>
+        <v>7493915</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>

--- a/artfynd/A 34441-2025 artfynd.xlsx
+++ b/artfynd/A 34441-2025 artfynd.xlsx
@@ -4564,10 +4564,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127497098</v>
+        <v>127497097</v>
       </c>
       <c r="B42" t="n">
-        <v>91372</v>
+        <v>57672</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4575,38 +4575,38 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Honkavaara, Nb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>864846</v>
+        <v>865211</v>
       </c>
       <c r="R42" t="n">
-        <v>7494223</v>
+        <v>7494097</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4641,13 +4641,17 @@
           <t>2025-08-13</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4666,10 +4670,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127497097</v>
+        <v>127497098</v>
       </c>
       <c r="B43" t="n">
-        <v>57672</v>
+        <v>91372</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4677,38 +4681,38 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Honkavaara, Nb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>865211</v>
+        <v>864846</v>
       </c>
       <c r="R43" t="n">
-        <v>7494097</v>
+        <v>7494223</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4743,17 +4747,13 @@
           <t>2025-08-13</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 34441-2025 artfynd.xlsx
+++ b/artfynd/A 34441-2025 artfynd.xlsx
@@ -4564,10 +4564,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127497097</v>
+        <v>127497098</v>
       </c>
       <c r="B42" t="n">
-        <v>57672</v>
+        <v>91372</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4575,38 +4575,38 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Honkavaara, Nb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>865211</v>
+        <v>864846</v>
       </c>
       <c r="R42" t="n">
-        <v>7494097</v>
+        <v>7494223</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4641,17 +4641,13 @@
           <t>2025-08-13</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4670,10 +4666,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127497098</v>
+        <v>127497097</v>
       </c>
       <c r="B43" t="n">
-        <v>91372</v>
+        <v>57672</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4681,38 +4677,38 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Honkavaara, Nb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>864846</v>
+        <v>865211</v>
       </c>
       <c r="R43" t="n">
-        <v>7494223</v>
+        <v>7494097</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4747,13 +4743,17 @@
           <t>2025-08-13</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 34441-2025 artfynd.xlsx
+++ b/artfynd/A 34441-2025 artfynd.xlsx
@@ -4461,7 +4461,7 @@
         <v>127497103</v>
       </c>
       <c r="B41" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>127497097</v>
       </c>
       <c r="B42" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4673,7 +4673,7 @@
         <v>127497098</v>
       </c>
       <c r="B43" t="n">
-        <v>91372</v>
+        <v>91380</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         <v>127497096</v>
       </c>
       <c r="B44" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 34441-2025 artfynd.xlsx
+++ b/artfynd/A 34441-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY44"/>
+  <dimension ref="A1:AY46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127497133</v>
+        <v>127497093</v>
       </c>
       <c r="B2" t="n">
-        <v>79029</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>865224</v>
+        <v>865005</v>
       </c>
       <c r="R2" t="n">
-        <v>7494121</v>
+        <v>7494058</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127497136</v>
+        <v>127497143</v>
       </c>
       <c r="B3" t="n">
-        <v>92642</v>
+        <v>93191</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>864673</v>
+        <v>865176</v>
       </c>
       <c r="R3" t="n">
-        <v>7493901</v>
+        <v>7494463</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127497100</v>
+        <v>127497135</v>
       </c>
       <c r="B4" t="n">
-        <v>80036</v>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>864814</v>
+        <v>864717</v>
       </c>
       <c r="R4" t="n">
-        <v>7494119</v>
+        <v>7493817</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127497110</v>
+        <v>127497136</v>
       </c>
       <c r="B5" t="n">
-        <v>80168</v>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>865019</v>
+        <v>864673</v>
       </c>
       <c r="R5" t="n">
-        <v>7494142</v>
+        <v>7493901</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127497134</v>
+        <v>127497137</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>865012</v>
+        <v>864714</v>
       </c>
       <c r="R6" t="n">
-        <v>7493915</v>
+        <v>7493998</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127497116</v>
+        <v>127497138</v>
       </c>
       <c r="B7" t="n">
-        <v>79029</v>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>864724</v>
+        <v>865258</v>
       </c>
       <c r="R7" t="n">
-        <v>7493953</v>
+        <v>7494241</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127497118</v>
+        <v>127497139</v>
       </c>
       <c r="B8" t="n">
-        <v>79029</v>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>864875</v>
+        <v>865258</v>
       </c>
       <c r="R8" t="n">
-        <v>7493981</v>
+        <v>7494165</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1354,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127497109</v>
+        <v>127497140</v>
       </c>
       <c r="B9" t="n">
-        <v>80168</v>
+        <v>93197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6464</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>864826</v>
+        <v>865254</v>
       </c>
       <c r="R9" t="n">
-        <v>7494067</v>
+        <v>7494165</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127497142</v>
+        <v>127497141</v>
       </c>
       <c r="B10" t="n">
-        <v>78007</v>
+        <v>93197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>864722</v>
+        <v>865108</v>
       </c>
       <c r="R10" t="n">
-        <v>7493992</v>
+        <v>7493903</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127497126</v>
+        <v>127497098</v>
       </c>
       <c r="B11" t="n">
-        <v>79029</v>
+        <v>91930</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,34 +1559,38 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Honkavaara, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>865024</v>
+        <v>864846</v>
       </c>
       <c r="R11" t="n">
-        <v>7494051</v>
+        <v>7494223</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1627,6 +1631,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1645,32 +1650,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127497141</v>
+        <v>127497116</v>
       </c>
       <c r="B12" t="n">
-        <v>92642</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>865108</v>
+        <v>864724</v>
       </c>
       <c r="R12" t="n">
-        <v>7493903</v>
+        <v>7493953</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1742,32 +1747,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127497144</v>
+        <v>127497117</v>
       </c>
       <c r="B13" t="n">
-        <v>78435</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>864722</v>
+        <v>864891</v>
       </c>
       <c r="R13" t="n">
-        <v>7493995</v>
+        <v>7493944</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1839,32 +1844,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127497093</v>
+        <v>127497118</v>
       </c>
       <c r="B14" t="n">
-        <v>91352</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>865005</v>
+        <v>864875</v>
       </c>
       <c r="R14" t="n">
-        <v>7494058</v>
+        <v>7493981</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1936,32 +1941,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127497111</v>
+        <v>127497119</v>
       </c>
       <c r="B15" t="n">
-        <v>58042</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,7 +1976,7 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>865056</v>
+        <v>864839</v>
       </c>
       <c r="R15" t="n">
         <v>7494049</v>
@@ -2033,32 +2038,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127497114</v>
+        <v>127497120</v>
       </c>
       <c r="B16" t="n">
-        <v>91370</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>865027</v>
+        <v>864828</v>
       </c>
       <c r="R16" t="n">
-        <v>7494163</v>
+        <v>7494091</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2130,32 +2135,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127497115</v>
+        <v>127497122</v>
       </c>
       <c r="B17" t="n">
-        <v>91370</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>865088</v>
+        <v>864916</v>
       </c>
       <c r="R17" t="n">
-        <v>7494361</v>
+        <v>7494217</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2227,14 +2232,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127497117</v>
+        <v>127497123</v>
       </c>
       <c r="B18" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2262,10 +2267,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>864891</v>
+        <v>864943</v>
       </c>
       <c r="R18" t="n">
-        <v>7493944</v>
+        <v>7494130</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2324,14 +2329,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127497120</v>
+        <v>127497124</v>
       </c>
       <c r="B19" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2359,10 +2364,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>864828</v>
+        <v>864971</v>
       </c>
       <c r="R19" t="n">
-        <v>7494091</v>
+        <v>7494087</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2421,32 +2426,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127497145</v>
+        <v>127497125</v>
       </c>
       <c r="B20" t="n">
-        <v>78435</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2456,10 +2461,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>865232</v>
+        <v>864993</v>
       </c>
       <c r="R20" t="n">
-        <v>7494161</v>
+        <v>7494054</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2518,32 +2523,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127497107</v>
+        <v>127497126</v>
       </c>
       <c r="B21" t="n">
-        <v>97353</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2553,10 +2558,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>864900</v>
+        <v>865024</v>
       </c>
       <c r="R21" t="n">
-        <v>7494240</v>
+        <v>7494051</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2615,32 +2620,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127497099</v>
+        <v>127497127</v>
       </c>
       <c r="B22" t="n">
-        <v>57669</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2650,10 +2655,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>865213</v>
+        <v>865064</v>
       </c>
       <c r="R22" t="n">
-        <v>7494422</v>
+        <v>7494185</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2712,14 +2717,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127497132</v>
+        <v>127497128</v>
       </c>
       <c r="B23" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2747,10 +2752,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>865208</v>
+        <v>864973</v>
       </c>
       <c r="R23" t="n">
-        <v>7494123</v>
+        <v>7494288</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2809,32 +2814,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127497143</v>
+        <v>127497129</v>
       </c>
       <c r="B24" t="n">
-        <v>92636</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4362</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2844,10 +2849,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>865176</v>
+        <v>865084</v>
       </c>
       <c r="R24" t="n">
-        <v>7494463</v>
+        <v>7494368</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2909,11 +2914,11 @@
         <v>127497130</v>
       </c>
       <c r="B25" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3003,32 +3008,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127497108</v>
+        <v>127497131</v>
       </c>
       <c r="B26" t="n">
-        <v>97353</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3038,10 +3043,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>865165</v>
+        <v>865118</v>
       </c>
       <c r="R26" t="n">
-        <v>7493982</v>
+        <v>7494428</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3100,14 +3105,14 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127497127</v>
+        <v>127497132</v>
       </c>
       <c r="B27" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3135,10 +3140,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>865064</v>
+        <v>865208</v>
       </c>
       <c r="R27" t="n">
-        <v>7494185</v>
+        <v>7494123</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3197,32 +3202,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127497137</v>
+        <v>127497133</v>
       </c>
       <c r="B28" t="n">
-        <v>92642</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3232,10 +3237,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>864714</v>
+        <v>865224</v>
       </c>
       <c r="R28" t="n">
-        <v>7493998</v>
+        <v>7494121</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3294,14 +3299,14 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127497131</v>
+        <v>127497134</v>
       </c>
       <c r="B29" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -3329,10 +3334,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>865118</v>
+        <v>865012</v>
       </c>
       <c r="R29" t="n">
-        <v>7494428</v>
+        <v>7493915</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3391,10 +3396,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127497119</v>
+        <v>127497144</v>
       </c>
       <c r="B30" t="n">
-        <v>79029</v>
+        <v>78730</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3402,21 +3407,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3426,10 +3431,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>864839</v>
+        <v>864722</v>
       </c>
       <c r="R30" t="n">
-        <v>7494049</v>
+        <v>7493995</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3488,32 +3493,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127497135</v>
+        <v>127497145</v>
       </c>
       <c r="B31" t="n">
-        <v>92642</v>
+        <v>78730</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3523,10 +3528,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>864717</v>
+        <v>865232</v>
       </c>
       <c r="R31" t="n">
-        <v>7493817</v>
+        <v>7494161</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3585,32 +3590,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127497129</v>
+        <v>127497100</v>
       </c>
       <c r="B32" t="n">
-        <v>79029</v>
+        <v>80336</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3620,10 +3625,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>865084</v>
+        <v>864814</v>
       </c>
       <c r="R32" t="n">
-        <v>7494368</v>
+        <v>7494119</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3682,32 +3687,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127497123</v>
+        <v>127497109</v>
       </c>
       <c r="B33" t="n">
-        <v>79029</v>
+        <v>80468</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3717,10 +3722,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>864943</v>
+        <v>864826</v>
       </c>
       <c r="R33" t="n">
-        <v>7494130</v>
+        <v>7494067</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3779,10 +3784,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127497140</v>
+        <v>127497110</v>
       </c>
       <c r="B34" t="n">
-        <v>92642</v>
+        <v>80468</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3790,21 +3795,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>6464</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3814,10 +3819,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>865254</v>
+        <v>865019</v>
       </c>
       <c r="R34" t="n">
-        <v>7494165</v>
+        <v>7494142</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3876,10 +3881,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127497122</v>
+        <v>127497142</v>
       </c>
       <c r="B35" t="n">
-        <v>79029</v>
+        <v>78334</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3887,21 +3892,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3911,10 +3916,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>864916</v>
+        <v>864722</v>
       </c>
       <c r="R35" t="n">
-        <v>7494217</v>
+        <v>7493992</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -3973,10 +3978,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127497106</v>
+        <v>127497099</v>
       </c>
       <c r="B36" t="n">
-        <v>97353</v>
+        <v>57950</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3984,21 +3989,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221941</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4008,10 +4013,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>864869</v>
+        <v>865213</v>
       </c>
       <c r="R36" t="n">
-        <v>7494274</v>
+        <v>7494422</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4070,45 +4075,53 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127497105</v>
+        <v>127497095</v>
       </c>
       <c r="B37" t="n">
-        <v>97353</v>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Honkavaara, Nb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>864754</v>
+        <v>864871</v>
       </c>
       <c r="R37" t="n">
-        <v>7493961</v>
+        <v>7493858</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4141,6 +4154,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färskt ringhack på tall.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4167,10 +4185,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127497128</v>
+        <v>127497096</v>
       </c>
       <c r="B38" t="n">
-        <v>79029</v>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4178,34 +4196,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Honkavaara, Nb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>864973</v>
+        <v>864944</v>
       </c>
       <c r="R38" t="n">
-        <v>7494288</v>
+        <v>7494143</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4238,6 +4264,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Färskt ringhack på tall.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4264,10 +4295,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127497124</v>
+        <v>127497097</v>
       </c>
       <c r="B39" t="n">
-        <v>79029</v>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4275,34 +4306,38 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Honkavaara, Nb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>864971</v>
+        <v>865211</v>
       </c>
       <c r="R39" t="n">
-        <v>7494087</v>
+        <v>7494097</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4335,6 +4370,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4361,10 +4401,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127497125</v>
+        <v>127497103</v>
       </c>
       <c r="B40" t="n">
-        <v>79029</v>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4372,34 +4412,38 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Honkavaara, Nb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>864993</v>
+        <v>865216</v>
       </c>
       <c r="R40" t="n">
-        <v>7494054</v>
+        <v>7494100</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4432,6 +4476,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, äldre.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4458,27 +4507,27 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127497103</v>
+        <v>127497111</v>
       </c>
       <c r="B41" t="n">
-        <v>57673</v>
+        <v>58327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4487,20 +4536,16 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Honkavaara, Nb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>865216</v>
+        <v>865056</v>
       </c>
       <c r="R41" t="n">
-        <v>7494100</v>
+        <v>7494049</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4533,11 +4578,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-13</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, äldre.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4564,49 +4604,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127497097</v>
+        <v>127497104</v>
       </c>
       <c r="B42" t="n">
-        <v>57673</v>
+        <v>97989</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Honkavaara, Nb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>865211</v>
+        <v>864719</v>
       </c>
       <c r="R42" t="n">
-        <v>7494097</v>
+        <v>7493805</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4639,11 +4675,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-13</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4670,49 +4701,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127497098</v>
+        <v>127497105</v>
       </c>
       <c r="B43" t="n">
-        <v>91380</v>
+        <v>97989</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5442</v>
+        <v>221941</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Honkavaara, Nb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>864846</v>
+        <v>864754</v>
       </c>
       <c r="R43" t="n">
-        <v>7494223</v>
+        <v>7493961</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4753,7 +4780,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4772,53 +4798,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127497096</v>
+        <v>127497106</v>
       </c>
       <c r="B44" t="n">
-        <v>57673</v>
+        <v>97989</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Honkavaara, Nb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>864944</v>
+        <v>864869</v>
       </c>
       <c r="R44" t="n">
-        <v>7494143</v>
+        <v>7494274</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4853,11 +4871,6 @@
           <t>2025-08-13</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Färskt ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -4879,6 +4892,200 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>127497107</v>
+      </c>
+      <c r="B45" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Honkavaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>864900</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7494240</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>127497108</v>
+      </c>
+      <c r="B46" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Honkavaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>865165</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7493982</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34441-2025 artfynd.xlsx
+++ b/artfynd/A 34441-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY46"/>
+  <dimension ref="A1:AZ46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127497093</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127497143</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127497135</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127497136</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127497137</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127497138</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127497139</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127497140</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127497141</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1647,6 +1697,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127497098</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1744,6 +1799,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127497116</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1841,6 +1901,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127497117</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1938,6 +2003,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127497118</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2035,6 +2105,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127497119</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2132,6 +2207,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127497120</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2229,6 +2309,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127497122</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2326,6 +2411,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127497123</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2423,6 +2513,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127497124</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2520,6 +2615,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127497125</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2617,6 +2717,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127497126</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2714,6 +2819,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127497127</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2811,6 +2921,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127497128</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2908,6 +3023,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127497129</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3005,6 +3125,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127497130</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3102,6 +3227,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127497131</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3199,6 +3329,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127497132</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3296,6 +3431,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127497133</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3393,6 +3533,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127497134</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3490,6 +3635,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127497144</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3587,6 +3737,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127497145</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3684,6 +3839,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127497100</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3781,6 +3941,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127497109</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3878,6 +4043,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127497110</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3975,6 +4145,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127497142</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4072,6 +4247,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127497099</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4182,6 +4362,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127497095</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4292,6 +4477,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127497096</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4398,6 +4588,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127497097</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4504,6 +4699,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127497103</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4601,6 +4801,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127497111</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4698,6 +4903,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127497104</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4795,6 +5005,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127497105</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4892,6 +5107,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127497106</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4989,6 +5209,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127497107</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5086,8 +5311,60 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127497108</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>